--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8">
@@ -964,7 +964,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>43.3%</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>80.1%</t>
         </is>
       </c>
     </row>
@@ -1318,22 +1318,22 @@
         <v>40</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>18</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>83.8%</t>
+          <t>84.9%</t>
         </is>
       </c>
     </row>
@@ -1400,22 +1400,22 @@
         <v>41</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>18</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>84.0%</t>
         </is>
       </c>
     </row>
@@ -1478,22 +1478,22 @@
         <v>40</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>18</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>72.2%</t>
         </is>
       </c>
     </row>
@@ -1560,22 +1560,22 @@
         <v>40</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>18</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>78.9%</t>
         </is>
       </c>
     </row>
@@ -1642,22 +1642,22 @@
         <v>40</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>18</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>78.8%</t>
         </is>
       </c>
     </row>
@@ -1724,22 +1724,22 @@
         <v>40</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>18</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>80.2%</t>
         </is>
       </c>
     </row>
@@ -1806,22 +1806,22 @@
         <v>40</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>18</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>85.4%</t>
+          <t>86.0%</t>
         </is>
       </c>
     </row>
@@ -2614,45 +2614,49 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>A2A1</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>37/37</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3780,45 +3784,49 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>A2A2</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E64" s="5" t="inlineStr">
         <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>27/35</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5771,45 +5779,49 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
         <is>
           <t>A2B1</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="C109" s="5" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="D109" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E109" s="5" t="inlineStr">
         <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>36/37</t>
+        </is>
+      </c>
+      <c r="I109" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7555,45 +7567,49 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
         <is>
           <t>A2B2</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
+      <c r="C149" s="5" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="D149" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E149" s="5" t="inlineStr">
         <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>0/36</t>
-        </is>
-      </c>
-      <c r="I149" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G149" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H149" s="5" t="inlineStr">
+        <is>
+          <t>34/36</t>
+        </is>
+      </c>
+      <c r="I149" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -8173,88 +8189,96 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
         <is>
           <t>A2C1</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
+      <c r="C163" s="5" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="D163" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E163" s="5" t="inlineStr">
         <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I163" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H163" s="5" t="inlineStr">
+        <is>
+          <t>10/37</t>
+        </is>
+      </c>
+      <c r="I163" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="A164" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B164" s="5" t="inlineStr">
         <is>
           <t>A2C1</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
+      <c r="C164" s="5" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="D164" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E164" s="5" t="inlineStr">
         <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I164" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F164" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G164" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H164" s="5" t="inlineStr">
+        <is>
+          <t>34/37</t>
+        </is>
+      </c>
+      <c r="I164" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9961,88 +9985,96 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B203" s="2" t="inlineStr">
+      <c r="A203" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B203" s="5" t="inlineStr">
         <is>
           <t>A2C2</t>
         </is>
       </c>
-      <c r="C203" s="2" t="inlineStr">
+      <c r="C203" s="5" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="D203" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="E203" s="5" t="inlineStr">
         <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="F203" s="2" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G203" s="2" t="inlineStr"/>
-      <c r="H203" s="2" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I203" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F203" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G203" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H203" s="5" t="inlineStr">
+        <is>
+          <t>11/37</t>
+        </is>
+      </c>
+      <c r="I203" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B204" s="2" t="inlineStr">
+      <c r="A204" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B204" s="5" t="inlineStr">
         <is>
           <t>A2C2</t>
         </is>
       </c>
-      <c r="C204" s="2" t="inlineStr">
+      <c r="C204" s="5" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D204" s="2" t="inlineStr">
+      <c r="D204" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="E204" s="5" t="inlineStr">
         <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="F204" s="2" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G204" s="2" t="inlineStr"/>
-      <c r="H204" s="2" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I204" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F204" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G204" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H204" s="5" t="inlineStr">
+        <is>
+          <t>35/37</t>
+        </is>
+      </c>
+      <c r="I204" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12258,45 +12290,49 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B254" s="2" t="inlineStr">
+      <c r="A254" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B254" s="5" t="inlineStr">
         <is>
           <t>A2D1</t>
         </is>
       </c>
-      <c r="C254" s="2" t="inlineStr">
+      <c r="C254" s="5" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D254" s="2" t="inlineStr">
+      <c r="D254" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E254" s="2" t="inlineStr">
+      <c r="E254" s="5" t="inlineStr">
         <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="F254" s="2" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G254" s="2" t="inlineStr"/>
-      <c r="H254" s="2" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I254" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F254" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G254" s="5" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="H254" s="5" t="inlineStr">
+        <is>
+          <t>33/34</t>
+        </is>
+      </c>
+      <c r="I254" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1105,7 +1105,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>160715@med.asu.edu.eg, 2025/2026</t>
+          <t>2025/2026, 160715@med.asu.edu.eg</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
@@ -11195,7 +11195,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11477,7 +11477,7 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>160715@med.asu.edu.eg, 2025/2026</t>
+          <t>2025/2026, 160715@med.asu.edu.eg</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -12311,7 +12311,7 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
@@ -12405,7 +12405,7 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr">
@@ -13019,7 +13019,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2025/2026</t>
+          <t>2025/2026, 2027/2028</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2027/2028, 2025/2026</t>
+          <t>2025/2026, 2027/2028, 2026/2027</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H295" s="5" t="inlineStr">
@@ -14827,7 +14827,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2025/2026</t>
+          <t>2025/2026, 2027/2028</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -14921,7 +14921,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2027/2028, 2025/2026</t>
+          <t>2025/2026, 2027/2028, 2026/2027</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
@@ -964,7 +964,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>50.2%</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>79.7%</t>
         </is>
       </c>
     </row>
@@ -1318,22 +1318,22 @@
         <v>40</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>15</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>83.9%</t>
         </is>
       </c>
     </row>
@@ -1400,22 +1400,22 @@
         <v>41</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>15</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>80.4%</t>
         </is>
       </c>
     </row>
@@ -1478,22 +1478,22 @@
         <v>40</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>73.7%</t>
         </is>
       </c>
     </row>
@@ -1560,22 +1560,22 @@
         <v>40</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>15</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>81.3%</t>
         </is>
       </c>
     </row>
@@ -1642,22 +1642,22 @@
         <v>40</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>15</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>79.8%</t>
         </is>
       </c>
     </row>
@@ -1724,22 +1724,22 @@
         <v>40</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>15</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>81.1%</t>
         </is>
       </c>
     </row>
@@ -1806,22 +1806,22 @@
         <v>40</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>15</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>86.6%</t>
+          <t>83.8%</t>
         </is>
       </c>
     </row>
@@ -1884,22 +1884,22 @@
         <v>40</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>15</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>74.6%</t>
         </is>
       </c>
     </row>
@@ -2755,45 +2755,49 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>A2A1</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>31/37</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3929,45 +3933,49 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>A2A2</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E67" s="5" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>11/35</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6104,45 +6112,49 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
         <is>
           <t>A2B1</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="C116" s="5" t="inlineStr">
         <is>
           <t>PHYSICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="D116" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E116" s="5" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="inlineStr">
+        <is>
+          <t>29/37</t>
+        </is>
+      </c>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7900,45 +7912,49 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="A156" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
         <is>
           <t>A2B2</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
+      <c r="C156" s="5" t="inlineStr">
         <is>
           <t>PHYSICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="D156" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E156" s="5" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>0/36</t>
-        </is>
-      </c>
-      <c r="I156" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F156" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G156" s="5" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="H156" s="5" t="inlineStr">
+        <is>
+          <t>34/36</t>
+        </is>
+      </c>
+      <c r="I156" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -8401,45 +8417,49 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="A167" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
         <is>
           <t>A2C1</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
+      <c r="C167" s="5" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="D167" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E167" s="5" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I167" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F167" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G167" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H167" s="5" t="inlineStr">
+        <is>
+          <t>31/37</t>
+        </is>
+      </c>
+      <c r="I167" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10201,45 +10221,49 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B207" s="2" t="inlineStr">
+      <c r="A207" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B207" s="5" t="inlineStr">
         <is>
           <t>A2C2</t>
         </is>
       </c>
-      <c r="C207" s="2" t="inlineStr">
+      <c r="C207" s="5" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D207" s="2" t="inlineStr">
+      <c r="D207" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="E207" s="5" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="F207" s="2" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G207" s="2" t="inlineStr"/>
-      <c r="H207" s="2" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I207" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F207" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G207" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H207" s="5" t="inlineStr">
+        <is>
+          <t>31/37</t>
+        </is>
+      </c>
+      <c r="I207" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12467,45 +12491,49 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B257" s="2" t="inlineStr">
+      <c r="A257" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B257" s="5" t="inlineStr">
         <is>
           <t>A2D1</t>
         </is>
       </c>
-      <c r="C257" s="2" t="inlineStr">
+      <c r="C257" s="5" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D257" s="2" t="inlineStr">
+      <c r="D257" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E257" s="2" t="inlineStr">
+      <c r="E257" s="5" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="F257" s="2" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G257" s="2" t="inlineStr"/>
-      <c r="H257" s="2" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I257" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F257" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G257" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026, 2026/2027</t>
+        </is>
+      </c>
+      <c r="H257" s="5" t="inlineStr">
+        <is>
+          <t>7/34</t>
+        </is>
+      </c>
+      <c r="I257" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13113,7 +13141,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027, 2027/2028</t>
+          <t>2025/2026, 2027/2028, 2026/2027</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -14275,45 +14303,49 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B297" s="2" t="inlineStr">
+      <c r="A297" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B297" s="5" t="inlineStr">
         <is>
           <t>A2D2</t>
         </is>
       </c>
-      <c r="C297" s="2" t="inlineStr">
+      <c r="C297" s="5" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D297" s="2" t="inlineStr">
+      <c r="D297" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E297" s="2" t="inlineStr">
+      <c r="E297" s="5" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="F297" s="2" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G297" s="2" t="inlineStr"/>
-      <c r="H297" s="2" t="inlineStr">
-        <is>
-          <t>0/40</t>
-        </is>
-      </c>
-      <c r="I297" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F297" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G297" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026, 2026/2027</t>
+        </is>
+      </c>
+      <c r="H297" s="5" t="inlineStr">
+        <is>
+          <t>19/40</t>
+        </is>
+      </c>
+      <c r="I297" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14921,7 +14953,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027, 2027/2028</t>
+          <t>2025/2026, 2027/2028, 2026/2027</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -13141,7 +13141,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2026/2027, 2025/2026</t>
+          <t>2026/2027, 2027/2028, 2025/2026</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -14953,7 +14953,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2026/2027, 2025/2026</t>
+          <t>2026/2027, 2027/2028, 2025/2026</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1105,7 +1105,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -5408,7 +5408,7 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
@@ -12335,7 +12335,7 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
@@ -12429,7 +12429,7 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H257" s="5" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13141,7 +13141,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2026/2027, 2025/2026</t>
+          <t>2026/2027, 2027/2028, 2025/2026</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -14147,7 +14147,7 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H295" s="5" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H297" s="5" t="inlineStr">
@@ -14859,7 +14859,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -14953,7 +14953,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2026/2027, 2025/2026</t>
+          <t>2026/2027, 2027/2028, 2025/2026</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
@@ -964,7 +964,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>52.3%</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>79.1%</t>
+          <t>79.2%</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1642,22 +1642,22 @@
         <v>40</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>14</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>80.1%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1724,22 +1724,22 @@
         <v>40</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>14</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>81.5%</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
@@ -7455,7 +7455,7 @@
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -7549,7 +7549,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -8480,45 +8480,49 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="A168" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
         <is>
           <t>A2C1</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
+      <c r="C168" s="5" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="D168" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E168" s="5" t="inlineStr">
         <is>
           <t>27/06/2026</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I168" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F168" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G168" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H168" s="5" t="inlineStr">
+        <is>
+          <t>32/37</t>
+        </is>
+      </c>
+      <c r="I168" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9431,7 +9435,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9713,7 +9717,7 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>160715@med.asu.edu.eg, 2025/2026</t>
+          <t>2025/2026, 160715@med.asu.edu.eg</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
@@ -10284,45 +10288,49 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B208" s="2" t="inlineStr">
+      <c r="A208" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B208" s="5" t="inlineStr">
         <is>
           <t>A2C2</t>
         </is>
       </c>
-      <c r="C208" s="2" t="inlineStr">
+      <c r="C208" s="5" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D208" s="2" t="inlineStr">
+      <c r="D208" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="E208" s="5" t="inlineStr">
         <is>
           <t>27/06/2026</t>
         </is>
       </c>
-      <c r="F208" s="2" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G208" s="2" t="inlineStr"/>
-      <c r="H208" s="2" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I208" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F208" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G208" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H208" s="5" t="inlineStr">
+        <is>
+          <t>33/37</t>
+        </is>
+      </c>
+      <c r="I208" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11235,7 +11243,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11517,7 +11525,7 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>160715@med.asu.edu.eg, 2025/2026</t>
+          <t>2025/2026, 160715@med.asu.edu.eg</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -12351,7 +12359,7 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
@@ -12445,7 +12453,7 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr">
@@ -12539,7 +12547,7 @@
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H257" s="5" t="inlineStr">
@@ -13063,7 +13071,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13110,7 +13118,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2025/2026</t>
+          <t>2025/2026, 2027/2028</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13157,7 +13165,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2027/2028, 2025/2026</t>
+          <t>2025/2026, 2026/2027, 2027/2028</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -14163,7 +14171,7 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
@@ -14257,7 +14265,7 @@
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H295" s="5" t="inlineStr">
@@ -14351,7 +14359,7 @@
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H297" s="5" t="inlineStr">
@@ -14879,7 +14887,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -14926,7 +14934,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2025/2026</t>
+          <t>2025/2026, 2027/2028</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -14973,7 +14981,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2027/2028, 2025/2026</t>
+          <t>2025/2026, 2026/2027, 2027/2028</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -13118,7 +13118,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2027/2028</t>
+          <t>2027/2028, 2025/2026</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13165,7 +13165,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026, 2027/2028</t>
+          <t>2027/2028, 2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -14934,7 +14934,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2027/2028</t>
+          <t>2027/2028, 2025/2026</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -14981,7 +14981,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026, 2027/2028</t>
+          <t>2027/2028, 2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -13233,7 +13233,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2027/2028, 2025/2026</t>
+          <t>2027/2028, 2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -15057,7 +15057,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2027/2028, 2025/2026</t>
+          <t>2027/2028, 2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -96,10 +96,10 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>193</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
@@ -964,7 +964,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>62.3%</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>78.9%</t>
         </is>
       </c>
     </row>
@@ -1318,17 +1318,17 @@
         <v>40</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P15" s="4" t="n">
         <v>8</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
@@ -1400,22 +1400,22 @@
         <v>41</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P16" s="4" t="n">
         <v>11</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>79.1%</t>
+          <t>79.5%</t>
         </is>
       </c>
     </row>
@@ -1478,22 +1478,22 @@
         <v>40</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P17" s="4" t="n">
         <v>4</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>76.0%</t>
         </is>
       </c>
     </row>
@@ -1560,22 +1560,22 @@
         <v>40</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P18" s="4" t="n">
         <v>5</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>83.1%</t>
+          <t>82.3%</t>
         </is>
       </c>
     </row>
@@ -1642,22 +1642,22 @@
         <v>40</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P19" s="4" t="n">
         <v>6</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>81.3%</t>
+          <t>80.2%</t>
         </is>
       </c>
     </row>
@@ -1724,22 +1724,22 @@
         <v>40</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P20" s="4" t="n">
         <v>7</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>81.9%</t>
         </is>
       </c>
     </row>
@@ -1809,10 +1809,10 @@
         <v>26</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1888,22 +1888,22 @@
         <v>40</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P22" s="4" t="n">
         <v>3</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>69.4%</t>
         </is>
       </c>
     </row>
@@ -2116,475 +2116,479 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>A2A1</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>04/07/2026</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>29/37</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>Session recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>A2A1</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr"/>
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="L27" s="7" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="inlineStr">
-        <is>
-          <t>Session recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>Session missed</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>A2A1</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr"/>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>0/37</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>Future session</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>A2A1</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr"/>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>0/37</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>A2A1</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr"/>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>0/37</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>A2A1</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>0/37</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>A2A1</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>0/37</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>A2A1</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr"/>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>0/37</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>A2A1</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>PHYSICAL MEDICINE</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr"/>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>0/37</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>A2A1</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>PHYSICAL MEDICINE</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>05/07/2026</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr"/>
-      <c r="H28" s="6" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr"/>
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-      <c r="L28" s="8" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t>Session missed</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>A2A1</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr"/>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="L29" s="9" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
-        <is>
-          <t>Future session</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>A2A1</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr"/>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>A2A1</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>11/07/2026</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>A2A1</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>A2A1</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>A2A1</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>14/07/2026</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr"/>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>A2A1</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>PHYSICAL MEDICINE</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="inlineStr"/>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>A2A1</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>PHYSICAL MEDICINE</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>15/07/2026</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr"/>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4000,430 +4004,434 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>A2A2</t>
         </is>
       </c>
-      <c r="C68" s="6" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D68" s="6" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="E68" s="5" t="inlineStr">
         <is>
           <t>04/07/2026</t>
         </is>
       </c>
-      <c r="F68" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr"/>
-      <c r="H68" s="6" t="inlineStr">
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>30/35</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>A2A2</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr"/>
+      <c r="H69" s="7" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I68" s="6" t="inlineStr">
+      <c r="I69" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
         <is>
           <t>A2A2</t>
         </is>
       </c>
-      <c r="C69" s="6" t="inlineStr">
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D69" s="6" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr"/>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>0/35</t>
+        </is>
+      </c>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>A2A2</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr"/>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>0/35</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>A2A2</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr"/>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>0/35</t>
+        </is>
+      </c>
+      <c r="I72" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>A2A2</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr"/>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>0/35</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>A2A2</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr"/>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>0/35</t>
+        </is>
+      </c>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>A2A2</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr"/>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>0/35</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>A2A2</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>PHYSICAL MEDICINE</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr"/>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>0/35</t>
+        </is>
+      </c>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>A2A2</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>PHYSICAL MEDICINE</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>05/07/2026</t>
-        </is>
-      </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr"/>
-      <c r="H69" s="6" t="inlineStr">
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr"/>
+      <c r="H77" s="7" t="inlineStr">
         <is>
           <t>0/35</t>
         </is>
       </c>
-      <c r="I69" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>A2A2</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="F70" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr"/>
-      <c r="H70" s="6" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I70" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>A2A2</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
-      <c r="F71" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G71" s="6" t="inlineStr"/>
-      <c r="H71" s="6" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>A2A2</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E72" s="6" t="inlineStr">
-        <is>
-          <t>11/07/2026</t>
-        </is>
-      </c>
-      <c r="F72" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G72" s="6" t="inlineStr"/>
-      <c r="H72" s="6" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I72" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>A2A2</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G73" s="6" t="inlineStr"/>
-      <c r="H73" s="6" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>A2A2</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F74" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr"/>
-      <c r="H74" s="6" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I74" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>A2A2</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="inlineStr">
-        <is>
-          <t>14/07/2026</t>
-        </is>
-      </c>
-      <c r="F75" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G75" s="6" t="inlineStr"/>
-      <c r="H75" s="6" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I75" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>A2A2</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>PHYSICAL MEDICINE</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E76" s="6" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
-      <c r="F76" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G76" s="6" t="inlineStr"/>
-      <c r="H76" s="6" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I76" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>A2A2</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>PHYSICAL MEDICINE</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t>15/07/2026</t>
-        </is>
-      </c>
-      <c r="F77" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G77" s="6" t="inlineStr"/>
-      <c r="H77" s="6" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I77" s="6" t="inlineStr">
+      <c r="I77" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4665,430 +4673,434 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
         <is>
           <t>A2B1</t>
         </is>
       </c>
-      <c r="C83" s="6" t="inlineStr">
+      <c r="C83" s="5" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D83" s="6" t="inlineStr">
+      <c r="D83" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="E83" s="5" t="inlineStr">
         <is>
           <t>04/07/2026</t>
         </is>
       </c>
-      <c r="F83" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G83" s="6" t="inlineStr"/>
-      <c r="H83" s="6" t="inlineStr">
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>25/37</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>A2B1</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>ENDOCRINOLOGY</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="inlineStr"/>
+      <c r="H84" s="7" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I83" s="6" t="inlineStr">
+      <c r="I84" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
         <is>
           <t>A2B1</t>
         </is>
       </c>
-      <c r="C84" s="6" t="inlineStr">
+      <c r="C85" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>05/07/2026</t>
-        </is>
-      </c>
-      <c r="F84" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="inlineStr"/>
-      <c r="H84" s="6" t="inlineStr">
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr"/>
+      <c r="H85" s="7" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I84" s="6" t="inlineStr">
+      <c r="I85" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
         <is>
           <t>A2B1</t>
         </is>
       </c>
-      <c r="C85" s="6" t="inlineStr">
+      <c r="C86" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="F85" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G85" s="6" t="inlineStr"/>
-      <c r="H85" s="6" t="inlineStr">
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="inlineStr"/>
+      <c r="H86" s="7" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I85" s="6" t="inlineStr">
+      <c r="I86" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
         <is>
           <t>A2B1</t>
         </is>
       </c>
-      <c r="C86" s="6" t="inlineStr">
+      <c r="C87" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E86" s="6" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
-      <c r="F86" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr"/>
-      <c r="H86" s="6" t="inlineStr">
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr"/>
+      <c r="H87" s="7" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I86" s="6" t="inlineStr">
+      <c r="I87" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
         <is>
           <t>A2B1</t>
         </is>
       </c>
-      <c r="C87" s="6" t="inlineStr">
+      <c r="C88" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
-      <c r="F87" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="inlineStr"/>
-      <c r="H87" s="6" t="inlineStr">
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="inlineStr"/>
+      <c r="H88" s="7" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I87" s="6" t="inlineStr">
+      <c r="I88" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
         <is>
           <t>A2B1</t>
         </is>
       </c>
-      <c r="C88" s="6" t="inlineStr">
+      <c r="C89" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E88" s="6" t="inlineStr">
-        <is>
-          <t>11/07/2026</t>
-        </is>
-      </c>
-      <c r="F88" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G88" s="6" t="inlineStr"/>
-      <c r="H88" s="6" t="inlineStr">
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="inlineStr"/>
+      <c r="H89" s="7" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I88" s="6" t="inlineStr">
+      <c r="I89" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
         <is>
           <t>A2B1</t>
         </is>
       </c>
-      <c r="C89" s="6" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="F89" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G89" s="6" t="inlineStr"/>
-      <c r="H89" s="6" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="inlineStr"/>
+      <c r="H90" s="7" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I89" s="6" t="inlineStr">
+      <c r="I90" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
         <is>
           <t>A2B1</t>
         </is>
       </c>
-      <c r="C90" s="6" t="inlineStr">
+      <c r="C91" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E90" s="6" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F90" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr"/>
-      <c r="H90" s="6" t="inlineStr">
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr"/>
+      <c r="H91" s="7" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I90" s="6" t="inlineStr">
+      <c r="I91" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
         <is>
           <t>A2B1</t>
         </is>
       </c>
-      <c r="C91" s="6" t="inlineStr">
+      <c r="C92" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E91" s="6" t="inlineStr">
-        <is>
-          <t>14/07/2026</t>
-        </is>
-      </c>
-      <c r="F91" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G91" s="6" t="inlineStr"/>
-      <c r="H91" s="6" t="inlineStr">
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="inlineStr"/>
+      <c r="H92" s="7" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I91" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>A2B1</t>
-        </is>
-      </c>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>ENDOCRINOLOGY</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E92" s="6" t="inlineStr">
-        <is>
-          <t>15/07/2026</t>
-        </is>
-      </c>
-      <c r="F92" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr"/>
-      <c r="H92" s="6" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I92" s="6" t="inlineStr">
+      <c r="I92" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6489,430 +6501,434 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B123" s="6" t="inlineStr">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
         <is>
           <t>A2B2</t>
         </is>
       </c>
-      <c r="C123" s="6" t="inlineStr">
+      <c r="C123" s="5" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D123" s="6" t="inlineStr">
+      <c r="D123" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="E123" s="5" t="inlineStr">
         <is>
           <t>04/07/2026</t>
         </is>
       </c>
-      <c r="F123" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G123" s="6" t="inlineStr"/>
-      <c r="H123" s="6" t="inlineStr">
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>22/36</t>
+        </is>
+      </c>
+      <c r="I123" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B124" s="7" t="inlineStr">
+        <is>
+          <t>A2B2</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="inlineStr">
+        <is>
+          <t>ENDOCRINOLOGY</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G124" s="7" t="inlineStr"/>
+      <c r="H124" s="7" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I123" s="6" t="inlineStr">
+      <c r="I124" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B124" s="6" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
         <is>
           <t>A2B2</t>
         </is>
       </c>
-      <c r="C124" s="6" t="inlineStr">
+      <c r="C125" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E124" s="6" t="inlineStr">
-        <is>
-          <t>05/07/2026</t>
-        </is>
-      </c>
-      <c r="F124" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G124" s="6" t="inlineStr"/>
-      <c r="H124" s="6" t="inlineStr">
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="inlineStr"/>
+      <c r="H125" s="7" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I124" s="6" t="inlineStr">
+      <c r="I125" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B126" s="7" t="inlineStr">
         <is>
           <t>A2B2</t>
         </is>
       </c>
-      <c r="C125" s="6" t="inlineStr">
+      <c r="C126" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D125" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E125" s="6" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="F125" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G125" s="6" t="inlineStr"/>
-      <c r="H125" s="6" t="inlineStr">
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="F126" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G126" s="7" t="inlineStr"/>
+      <c r="H126" s="7" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I125" s="6" t="inlineStr">
+      <c r="I126" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B126" s="6" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B127" s="7" t="inlineStr">
         <is>
           <t>A2B2</t>
         </is>
       </c>
-      <c r="C126" s="6" t="inlineStr">
+      <c r="C127" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E126" s="6" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
-      <c r="F126" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G126" s="6" t="inlineStr"/>
-      <c r="H126" s="6" t="inlineStr">
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr"/>
+      <c r="H127" s="7" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I126" s="6" t="inlineStr">
+      <c r="I127" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B127" s="6" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B128" s="7" t="inlineStr">
         <is>
           <t>A2B2</t>
         </is>
       </c>
-      <c r="C127" s="6" t="inlineStr">
+      <c r="C128" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D127" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E127" s="6" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
-      <c r="F127" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G127" s="6" t="inlineStr"/>
-      <c r="H127" s="6" t="inlineStr">
+      <c r="D128" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="F128" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G128" s="7" t="inlineStr"/>
+      <c r="H128" s="7" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I127" s="6" t="inlineStr">
+      <c r="I128" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B128" s="6" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B129" s="7" t="inlineStr">
         <is>
           <t>A2B2</t>
         </is>
       </c>
-      <c r="C128" s="6" t="inlineStr">
+      <c r="C129" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D128" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E128" s="6" t="inlineStr">
-        <is>
-          <t>11/07/2026</t>
-        </is>
-      </c>
-      <c r="F128" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G128" s="6" t="inlineStr"/>
-      <c r="H128" s="6" t="inlineStr">
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="inlineStr"/>
+      <c r="H129" s="7" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I128" s="6" t="inlineStr">
+      <c r="I129" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B130" s="7" t="inlineStr">
         <is>
           <t>A2B2</t>
         </is>
       </c>
-      <c r="C129" s="6" t="inlineStr">
+      <c r="C130" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D129" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E129" s="6" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="F129" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G129" s="6" t="inlineStr"/>
-      <c r="H129" s="6" t="inlineStr">
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F130" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G130" s="7" t="inlineStr"/>
+      <c r="H130" s="7" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I129" s="6" t="inlineStr">
+      <c r="I130" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B130" s="6" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="inlineStr">
         <is>
           <t>A2B2</t>
         </is>
       </c>
-      <c r="C130" s="6" t="inlineStr">
+      <c r="C131" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D130" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E130" s="6" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F130" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G130" s="6" t="inlineStr"/>
-      <c r="H130" s="6" t="inlineStr">
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="inlineStr"/>
+      <c r="H131" s="7" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I130" s="6" t="inlineStr">
+      <c r="I131" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B131" s="6" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B132" s="7" t="inlineStr">
         <is>
           <t>A2B2</t>
         </is>
       </c>
-      <c r="C131" s="6" t="inlineStr">
+      <c r="C132" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D131" s="6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E131" s="6" t="inlineStr">
-        <is>
-          <t>14/07/2026</t>
-        </is>
-      </c>
-      <c r="F131" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G131" s="6" t="inlineStr"/>
-      <c r="H131" s="6" t="inlineStr">
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+      <c r="F132" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="inlineStr"/>
+      <c r="H132" s="7" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I131" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B132" s="6" t="inlineStr">
-        <is>
-          <t>A2B2</t>
-        </is>
-      </c>
-      <c r="C132" s="6" t="inlineStr">
-        <is>
-          <t>ENDOCRINOLOGY</t>
-        </is>
-      </c>
-      <c r="D132" s="6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E132" s="6" t="inlineStr">
-        <is>
-          <t>15/07/2026</t>
-        </is>
-      </c>
-      <c r="F132" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G132" s="6" t="inlineStr"/>
-      <c r="H132" s="6" t="inlineStr">
-        <is>
-          <t>0/36</t>
-        </is>
-      </c>
-      <c r="I132" s="6" t="inlineStr">
+      <c r="I132" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8767,430 +8783,434 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B173" s="6" t="inlineStr">
+      <c r="A173" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B173" s="5" t="inlineStr">
         <is>
           <t>A2C1</t>
         </is>
       </c>
-      <c r="C173" s="6" t="inlineStr">
+      <c r="C173" s="5" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D173" s="6" t="inlineStr">
+      <c r="D173" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E173" s="6" t="inlineStr">
+      <c r="E173" s="5" t="inlineStr">
         <is>
           <t>04/07/2026</t>
         </is>
       </c>
-      <c r="F173" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G173" s="6" t="inlineStr"/>
-      <c r="H173" s="6" t="inlineStr">
+      <c r="F173" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G173" s="5" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="H173" s="5" t="inlineStr">
+        <is>
+          <t>20/37</t>
+        </is>
+      </c>
+      <c r="I173" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B174" s="7" t="inlineStr">
+        <is>
+          <t>A2C1</t>
+        </is>
+      </c>
+      <c r="C174" s="7" t="inlineStr">
+        <is>
+          <t>GASTROENTEROLOGY</t>
+        </is>
+      </c>
+      <c r="D174" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E174" s="7" t="inlineStr">
+        <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="F174" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G174" s="7" t="inlineStr"/>
+      <c r="H174" s="7" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I173" s="6" t="inlineStr">
+      <c r="I174" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B174" s="6" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B175" s="7" t="inlineStr">
         <is>
           <t>A2C1</t>
         </is>
       </c>
-      <c r="C174" s="6" t="inlineStr">
+      <c r="C175" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D174" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E174" s="6" t="inlineStr">
-        <is>
-          <t>05/07/2026</t>
-        </is>
-      </c>
-      <c r="F174" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G174" s="6" t="inlineStr"/>
-      <c r="H174" s="6" t="inlineStr">
+      <c r="D175" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E175" s="7" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F175" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G175" s="7" t="inlineStr"/>
+      <c r="H175" s="7" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I174" s="6" t="inlineStr">
+      <c r="I175" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B175" s="6" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B176" s="7" t="inlineStr">
         <is>
           <t>A2C1</t>
         </is>
       </c>
-      <c r="C175" s="6" t="inlineStr">
+      <c r="C176" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D175" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E175" s="6" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="F175" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G175" s="6" t="inlineStr"/>
-      <c r="H175" s="6" t="inlineStr">
+      <c r="D176" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="F176" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G176" s="7" t="inlineStr"/>
+      <c r="H176" s="7" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I175" s="6" t="inlineStr">
+      <c r="I176" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B176" s="6" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B177" s="7" t="inlineStr">
         <is>
           <t>A2C1</t>
         </is>
       </c>
-      <c r="C176" s="6" t="inlineStr">
+      <c r="C177" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D176" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E176" s="6" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
-      <c r="F176" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G176" s="6" t="inlineStr"/>
-      <c r="H176" s="6" t="inlineStr">
+      <c r="D177" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E177" s="7" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="F177" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G177" s="7" t="inlineStr"/>
+      <c r="H177" s="7" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I176" s="6" t="inlineStr">
+      <c r="I177" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B177" s="6" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B178" s="7" t="inlineStr">
         <is>
           <t>A2C1</t>
         </is>
       </c>
-      <c r="C177" s="6" t="inlineStr">
+      <c r="C178" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D177" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E177" s="6" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
-      <c r="F177" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G177" s="6" t="inlineStr"/>
-      <c r="H177" s="6" t="inlineStr">
+      <c r="D178" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E178" s="7" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="F178" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G178" s="7" t="inlineStr"/>
+      <c r="H178" s="7" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I177" s="6" t="inlineStr">
+      <c r="I178" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B178" s="6" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B179" s="7" t="inlineStr">
         <is>
           <t>A2C1</t>
         </is>
       </c>
-      <c r="C178" s="6" t="inlineStr">
+      <c r="C179" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D178" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E178" s="6" t="inlineStr">
-        <is>
-          <t>11/07/2026</t>
-        </is>
-      </c>
-      <c r="F178" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G178" s="6" t="inlineStr"/>
-      <c r="H178" s="6" t="inlineStr">
+      <c r="D179" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E179" s="7" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="F179" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G179" s="7" t="inlineStr"/>
+      <c r="H179" s="7" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I178" s="6" t="inlineStr">
+      <c r="I179" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B179" s="6" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B180" s="7" t="inlineStr">
         <is>
           <t>A2C1</t>
         </is>
       </c>
-      <c r="C179" s="6" t="inlineStr">
+      <c r="C180" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D179" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E179" s="6" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="F179" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G179" s="6" t="inlineStr"/>
-      <c r="H179" s="6" t="inlineStr">
+      <c r="D180" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E180" s="7" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F180" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G180" s="7" t="inlineStr"/>
+      <c r="H180" s="7" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I179" s="6" t="inlineStr">
+      <c r="I180" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B180" s="6" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B181" s="7" t="inlineStr">
         <is>
           <t>A2C1</t>
         </is>
       </c>
-      <c r="C180" s="6" t="inlineStr">
+      <c r="C181" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D180" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E180" s="6" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F180" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G180" s="6" t="inlineStr"/>
-      <c r="H180" s="6" t="inlineStr">
+      <c r="D181" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E181" s="7" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="F181" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G181" s="7" t="inlineStr"/>
+      <c r="H181" s="7" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I180" s="6" t="inlineStr">
+      <c r="I181" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B181" s="6" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B182" s="7" t="inlineStr">
         <is>
           <t>A2C1</t>
         </is>
       </c>
-      <c r="C181" s="6" t="inlineStr">
+      <c r="C182" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D181" s="6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E181" s="6" t="inlineStr">
-        <is>
-          <t>14/07/2026</t>
-        </is>
-      </c>
-      <c r="F181" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G181" s="6" t="inlineStr"/>
-      <c r="H181" s="6" t="inlineStr">
+      <c r="D182" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E182" s="7" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+      <c r="F182" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G182" s="7" t="inlineStr"/>
+      <c r="H182" s="7" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I181" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B182" s="6" t="inlineStr">
-        <is>
-          <t>A2C1</t>
-        </is>
-      </c>
-      <c r="C182" s="6" t="inlineStr">
-        <is>
-          <t>GASTROENTEROLOGY</t>
-        </is>
-      </c>
-      <c r="D182" s="6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E182" s="6" t="inlineStr">
-        <is>
-          <t>15/07/2026</t>
-        </is>
-      </c>
-      <c r="F182" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G182" s="6" t="inlineStr"/>
-      <c r="H182" s="6" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I182" s="6" t="inlineStr">
+      <c r="I182" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9785,7 +9805,7 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>160715@med.asu.edu.eg, 2025/2026</t>
+          <t>2025/2026, 160715@med.asu.edu.eg</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
@@ -10583,430 +10603,434 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B213" s="6" t="inlineStr">
+      <c r="A213" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B213" s="5" t="inlineStr">
         <is>
           <t>A2C2</t>
         </is>
       </c>
-      <c r="C213" s="6" t="inlineStr">
+      <c r="C213" s="5" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D213" s="6" t="inlineStr">
+      <c r="D213" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E213" s="6" t="inlineStr">
+      <c r="E213" s="5" t="inlineStr">
         <is>
           <t>04/07/2026</t>
         </is>
       </c>
-      <c r="F213" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G213" s="6" t="inlineStr"/>
-      <c r="H213" s="6" t="inlineStr">
+      <c r="F213" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G213" s="5" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="H213" s="5" t="inlineStr">
+        <is>
+          <t>28/37</t>
+        </is>
+      </c>
+      <c r="I213" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B214" s="7" t="inlineStr">
+        <is>
+          <t>A2C2</t>
+        </is>
+      </c>
+      <c r="C214" s="7" t="inlineStr">
+        <is>
+          <t>GASTROENTEROLOGY</t>
+        </is>
+      </c>
+      <c r="D214" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E214" s="7" t="inlineStr">
+        <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="F214" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G214" s="7" t="inlineStr"/>
+      <c r="H214" s="7" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I213" s="6" t="inlineStr">
+      <c r="I214" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B214" s="6" t="inlineStr">
+    <row r="215">
+      <c r="A215" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B215" s="7" t="inlineStr">
         <is>
           <t>A2C2</t>
         </is>
       </c>
-      <c r="C214" s="6" t="inlineStr">
+      <c r="C215" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D214" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E214" s="6" t="inlineStr">
-        <is>
-          <t>05/07/2026</t>
-        </is>
-      </c>
-      <c r="F214" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G214" s="6" t="inlineStr"/>
-      <c r="H214" s="6" t="inlineStr">
+      <c r="D215" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E215" s="7" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F215" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G215" s="7" t="inlineStr"/>
+      <c r="H215" s="7" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I214" s="6" t="inlineStr">
+      <c r="I215" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B215" s="6" t="inlineStr">
+    <row r="216">
+      <c r="A216" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B216" s="7" t="inlineStr">
         <is>
           <t>A2C2</t>
         </is>
       </c>
-      <c r="C215" s="6" t="inlineStr">
+      <c r="C216" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D215" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E215" s="6" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="F215" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G215" s="6" t="inlineStr"/>
-      <c r="H215" s="6" t="inlineStr">
+      <c r="D216" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E216" s="7" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="F216" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G216" s="7" t="inlineStr"/>
+      <c r="H216" s="7" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I215" s="6" t="inlineStr">
+      <c r="I216" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B216" s="6" t="inlineStr">
+    <row r="217">
+      <c r="A217" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B217" s="7" t="inlineStr">
         <is>
           <t>A2C2</t>
         </is>
       </c>
-      <c r="C216" s="6" t="inlineStr">
+      <c r="C217" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D216" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E216" s="6" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
-      <c r="F216" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G216" s="6" t="inlineStr"/>
-      <c r="H216" s="6" t="inlineStr">
+      <c r="D217" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E217" s="7" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="F217" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G217" s="7" t="inlineStr"/>
+      <c r="H217" s="7" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I216" s="6" t="inlineStr">
+      <c r="I217" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B217" s="6" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B218" s="7" t="inlineStr">
         <is>
           <t>A2C2</t>
         </is>
       </c>
-      <c r="C217" s="6" t="inlineStr">
+      <c r="C218" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D217" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E217" s="6" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
-      <c r="F217" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G217" s="6" t="inlineStr"/>
-      <c r="H217" s="6" t="inlineStr">
+      <c r="D218" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E218" s="7" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="F218" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G218" s="7" t="inlineStr"/>
+      <c r="H218" s="7" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I217" s="6" t="inlineStr">
+      <c r="I218" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B218" s="6" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B219" s="7" t="inlineStr">
         <is>
           <t>A2C2</t>
         </is>
       </c>
-      <c r="C218" s="6" t="inlineStr">
+      <c r="C219" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D218" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E218" s="6" t="inlineStr">
-        <is>
-          <t>11/07/2026</t>
-        </is>
-      </c>
-      <c r="F218" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G218" s="6" t="inlineStr"/>
-      <c r="H218" s="6" t="inlineStr">
+      <c r="D219" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E219" s="7" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="F219" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G219" s="7" t="inlineStr"/>
+      <c r="H219" s="7" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I218" s="6" t="inlineStr">
+      <c r="I219" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B219" s="6" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B220" s="7" t="inlineStr">
         <is>
           <t>A2C2</t>
         </is>
       </c>
-      <c r="C219" s="6" t="inlineStr">
+      <c r="C220" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D219" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E219" s="6" t="inlineStr">
-        <is>
-          <t>12/07/2026</t>
-        </is>
-      </c>
-      <c r="F219" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G219" s="6" t="inlineStr"/>
-      <c r="H219" s="6" t="inlineStr">
+      <c r="D220" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E220" s="7" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="F220" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G220" s="7" t="inlineStr"/>
+      <c r="H220" s="7" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I219" s="6" t="inlineStr">
+      <c r="I220" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B220" s="6" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B221" s="7" t="inlineStr">
         <is>
           <t>A2C2</t>
         </is>
       </c>
-      <c r="C220" s="6" t="inlineStr">
+      <c r="C221" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D220" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E220" s="6" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="F220" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G220" s="6" t="inlineStr"/>
-      <c r="H220" s="6" t="inlineStr">
+      <c r="D221" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E221" s="7" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="F221" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G221" s="7" t="inlineStr"/>
+      <c r="H221" s="7" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I220" s="6" t="inlineStr">
+      <c r="I221" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B221" s="6" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B222" s="7" t="inlineStr">
         <is>
           <t>A2C2</t>
         </is>
       </c>
-      <c r="C221" s="6" t="inlineStr">
+      <c r="C222" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D221" s="6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E221" s="6" t="inlineStr">
-        <is>
-          <t>14/07/2026</t>
-        </is>
-      </c>
-      <c r="F221" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G221" s="6" t="inlineStr"/>
-      <c r="H221" s="6" t="inlineStr">
+      <c r="D222" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E222" s="7" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+      <c r="F222" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G222" s="7" t="inlineStr"/>
+      <c r="H222" s="7" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I221" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B222" s="6" t="inlineStr">
-        <is>
-          <t>A2C2</t>
-        </is>
-      </c>
-      <c r="C222" s="6" t="inlineStr">
-        <is>
-          <t>GASTROENTEROLOGY</t>
-        </is>
-      </c>
-      <c r="D222" s="6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E222" s="6" t="inlineStr">
-        <is>
-          <t>15/07/2026</t>
-        </is>
-      </c>
-      <c r="F222" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G222" s="6" t="inlineStr"/>
-      <c r="H222" s="6" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I222" s="6" t="inlineStr">
+      <c r="I222" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -11601,7 +11625,7 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>160715@med.asu.edu.eg, 2025/2026</t>
+          <t>2025/2026, 160715@med.asu.edu.eg</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -12865,215 +12889,215 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B263" s="6" t="inlineStr">
+      <c r="A263" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B263" s="7" t="inlineStr">
         <is>
           <t>A2D1</t>
         </is>
       </c>
-      <c r="C263" s="6" t="inlineStr">
+      <c r="C263" s="7" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D263" s="6" t="inlineStr">
+      <c r="D263" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E263" s="6" t="inlineStr">
+      <c r="E263" s="7" t="inlineStr">
         <is>
           <t>11/07/2026</t>
         </is>
       </c>
-      <c r="F263" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G263" s="6" t="inlineStr"/>
-      <c r="H263" s="6" t="inlineStr">
+      <c r="F263" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G263" s="7" t="inlineStr"/>
+      <c r="H263" s="7" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I263" s="6" t="inlineStr">
+      <c r="I263" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B264" s="6" t="inlineStr">
+      <c r="A264" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B264" s="7" t="inlineStr">
         <is>
           <t>A2D1</t>
         </is>
       </c>
-      <c r="C264" s="6" t="inlineStr">
+      <c r="C264" s="7" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D264" s="6" t="inlineStr">
+      <c r="D264" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E264" s="6" t="inlineStr">
+      <c r="E264" s="7" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="F264" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G264" s="6" t="inlineStr"/>
-      <c r="H264" s="6" t="inlineStr">
+      <c r="F264" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G264" s="7" t="inlineStr"/>
+      <c r="H264" s="7" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I264" s="6" t="inlineStr">
+      <c r="I264" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B265" s="6" t="inlineStr">
+      <c r="A265" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B265" s="7" t="inlineStr">
         <is>
           <t>A2D1</t>
         </is>
       </c>
-      <c r="C265" s="6" t="inlineStr">
+      <c r="C265" s="7" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D265" s="6" t="inlineStr">
+      <c r="D265" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E265" s="6" t="inlineStr">
+      <c r="E265" s="7" t="inlineStr">
         <is>
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="F265" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G265" s="6" t="inlineStr"/>
-      <c r="H265" s="6" t="inlineStr">
+      <c r="F265" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G265" s="7" t="inlineStr"/>
+      <c r="H265" s="7" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I265" s="6" t="inlineStr">
+      <c r="I265" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B266" s="6" t="inlineStr">
+      <c r="A266" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B266" s="7" t="inlineStr">
         <is>
           <t>A2D1</t>
         </is>
       </c>
-      <c r="C266" s="6" t="inlineStr">
+      <c r="C266" s="7" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D266" s="6" t="inlineStr">
+      <c r="D266" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E266" s="6" t="inlineStr">
+      <c r="E266" s="7" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F266" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G266" s="6" t="inlineStr"/>
-      <c r="H266" s="6" t="inlineStr">
+      <c r="F266" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G266" s="7" t="inlineStr"/>
+      <c r="H266" s="7" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I266" s="6" t="inlineStr">
+      <c r="I266" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B267" s="6" t="inlineStr">
+      <c r="A267" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B267" s="7" t="inlineStr">
         <is>
           <t>A2D1</t>
         </is>
       </c>
-      <c r="C267" s="6" t="inlineStr">
+      <c r="C267" s="7" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D267" s="6" t="inlineStr">
+      <c r="D267" s="7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E267" s="6" t="inlineStr">
+      <c r="E267" s="7" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F267" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G267" s="6" t="inlineStr"/>
-      <c r="H267" s="6" t="inlineStr">
+      <c r="F267" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G267" s="7" t="inlineStr"/>
+      <c r="H267" s="7" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I267" s="6" t="inlineStr">
+      <c r="I267" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -13206,7 +13230,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2027/2028</t>
+          <t>2027/2028, 2025/2026</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13253,7 +13277,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026, 2027/2028</t>
+          <t>2027/2028, 2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -13546,215 +13570,215 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B278" s="6" t="inlineStr">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
         <is>
           <t>A2D1</t>
         </is>
       </c>
-      <c r="C278" s="6" t="inlineStr">
+      <c r="C278" s="2" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D278" s="6" t="inlineStr">
+      <c r="D278" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E278" s="6" t="inlineStr">
+      <c r="E278" s="2" t="inlineStr">
         <is>
           <t>04/07/2026</t>
         </is>
       </c>
-      <c r="F278" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G278" s="6" t="inlineStr"/>
-      <c r="H278" s="6" t="inlineStr">
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G278" s="2" t="inlineStr"/>
+      <c r="H278" s="2" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I278" s="6" t="inlineStr">
+      <c r="I278" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B279" s="7" t="inlineStr">
+        <is>
+          <t>A2D1</t>
+        </is>
+      </c>
+      <c r="C279" s="7" t="inlineStr">
+        <is>
+          <t>RHEUMATOLOGY</t>
+        </is>
+      </c>
+      <c r="D279" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E279" s="7" t="inlineStr">
+        <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="F279" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G279" s="7" t="inlineStr"/>
+      <c r="H279" s="7" t="inlineStr">
+        <is>
+          <t>0/34</t>
+        </is>
+      </c>
+      <c r="I279" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="279">
-      <c r="A279" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B279" s="6" t="inlineStr">
+    <row r="280">
+      <c r="A280" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B280" s="7" t="inlineStr">
         <is>
           <t>A2D1</t>
         </is>
       </c>
-      <c r="C279" s="6" t="inlineStr">
+      <c r="C280" s="7" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D279" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E279" s="6" t="inlineStr">
-        <is>
-          <t>05/07/2026</t>
-        </is>
-      </c>
-      <c r="F279" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G279" s="6" t="inlineStr"/>
-      <c r="H279" s="6" t="inlineStr">
+      <c r="D280" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E280" s="7" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F280" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G280" s="7" t="inlineStr"/>
+      <c r="H280" s="7" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I279" s="6" t="inlineStr">
+      <c r="I280" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="280">
-      <c r="A280" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B280" s="6" t="inlineStr">
+    <row r="281">
+      <c r="A281" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B281" s="7" t="inlineStr">
         <is>
           <t>A2D1</t>
         </is>
       </c>
-      <c r="C280" s="6" t="inlineStr">
+      <c r="C281" s="7" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D280" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E280" s="6" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="F280" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G280" s="6" t="inlineStr"/>
-      <c r="H280" s="6" t="inlineStr">
+      <c r="D281" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E281" s="7" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="F281" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G281" s="7" t="inlineStr"/>
+      <c r="H281" s="7" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I280" s="6" t="inlineStr">
+      <c r="I281" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="281">
-      <c r="A281" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B281" s="6" t="inlineStr">
+    <row r="282">
+      <c r="A282" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B282" s="7" t="inlineStr">
         <is>
           <t>A2D1</t>
         </is>
       </c>
-      <c r="C281" s="6" t="inlineStr">
+      <c r="C282" s="7" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D281" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E281" s="6" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
-      <c r="F281" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G281" s="6" t="inlineStr"/>
-      <c r="H281" s="6" t="inlineStr">
+      <c r="D282" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E282" s="7" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="F282" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G282" s="7" t="inlineStr"/>
+      <c r="H282" s="7" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I281" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B282" s="6" t="inlineStr">
-        <is>
-          <t>A2D1</t>
-        </is>
-      </c>
-      <c r="C282" s="6" t="inlineStr">
-        <is>
-          <t>RHEUMATOLOGY</t>
-        </is>
-      </c>
-      <c r="D282" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E282" s="6" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
-      <c r="F282" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G282" s="6" t="inlineStr"/>
-      <c r="H282" s="6" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I282" s="6" t="inlineStr">
+      <c r="I282" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -14693,215 +14717,219 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B303" s="6" t="inlineStr">
+      <c r="A303" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B303" s="5" t="inlineStr">
         <is>
           <t>A2D2</t>
         </is>
       </c>
-      <c r="C303" s="6" t="inlineStr">
+      <c r="C303" s="5" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D303" s="6" t="inlineStr">
+      <c r="D303" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E303" s="6" t="inlineStr">
+      <c r="E303" s="5" t="inlineStr">
         <is>
           <t>04/07/2026</t>
         </is>
       </c>
-      <c r="F303" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G303" s="6" t="inlineStr"/>
-      <c r="H303" s="6" t="inlineStr">
+      <c r="F303" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G303" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H303" s="5" t="inlineStr">
+        <is>
+          <t>14/40</t>
+        </is>
+      </c>
+      <c r="I303" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B304" s="7" t="inlineStr">
+        <is>
+          <t>A2D2</t>
+        </is>
+      </c>
+      <c r="C304" s="7" t="inlineStr">
+        <is>
+          <t>NEPHROLOGY</t>
+        </is>
+      </c>
+      <c r="D304" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E304" s="7" t="inlineStr">
+        <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="F304" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G304" s="7" t="inlineStr"/>
+      <c r="H304" s="7" t="inlineStr">
         <is>
           <t>0/40</t>
         </is>
       </c>
-      <c r="I303" s="6" t="inlineStr">
+      <c r="I304" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="304">
-      <c r="A304" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B304" s="6" t="inlineStr">
+    <row r="305">
+      <c r="A305" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B305" s="7" t="inlineStr">
         <is>
           <t>A2D2</t>
         </is>
       </c>
-      <c r="C304" s="6" t="inlineStr">
+      <c r="C305" s="7" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D304" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E304" s="6" t="inlineStr">
-        <is>
-          <t>05/07/2026</t>
-        </is>
-      </c>
-      <c r="F304" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G304" s="6" t="inlineStr"/>
-      <c r="H304" s="6" t="inlineStr">
+      <c r="D305" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E305" s="7" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="F305" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G305" s="7" t="inlineStr"/>
+      <c r="H305" s="7" t="inlineStr">
         <is>
           <t>0/40</t>
         </is>
       </c>
-      <c r="I304" s="6" t="inlineStr">
+      <c r="I305" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="305">
-      <c r="A305" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B305" s="6" t="inlineStr">
+    <row r="306">
+      <c r="A306" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B306" s="7" t="inlineStr">
         <is>
           <t>A2D2</t>
         </is>
       </c>
-      <c r="C305" s="6" t="inlineStr">
+      <c r="C306" s="7" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D305" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E305" s="6" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="F305" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G305" s="6" t="inlineStr"/>
-      <c r="H305" s="6" t="inlineStr">
+      <c r="D306" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E306" s="7" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="F306" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G306" s="7" t="inlineStr"/>
+      <c r="H306" s="7" t="inlineStr">
         <is>
           <t>0/40</t>
         </is>
       </c>
-      <c r="I305" s="6" t="inlineStr">
+      <c r="I306" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="306">
-      <c r="A306" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B306" s="6" t="inlineStr">
+    <row r="307">
+      <c r="A307" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B307" s="7" t="inlineStr">
         <is>
           <t>A2D2</t>
         </is>
       </c>
-      <c r="C306" s="6" t="inlineStr">
+      <c r="C307" s="7" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D306" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E306" s="6" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
-      <c r="F306" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G306" s="6" t="inlineStr"/>
-      <c r="H306" s="6" t="inlineStr">
+      <c r="D307" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E307" s="7" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="F307" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G307" s="7" t="inlineStr"/>
+      <c r="H307" s="7" t="inlineStr">
         <is>
           <t>0/40</t>
         </is>
       </c>
-      <c r="I306" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B307" s="6" t="inlineStr">
-        <is>
-          <t>A2D2</t>
-        </is>
-      </c>
-      <c r="C307" s="6" t="inlineStr">
-        <is>
-          <t>NEPHROLOGY</t>
-        </is>
-      </c>
-      <c r="D307" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E307" s="6" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
-      <c r="F307" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G307" s="6" t="inlineStr"/>
-      <c r="H307" s="6" t="inlineStr">
-        <is>
-          <t>0/40</t>
-        </is>
-      </c>
-      <c r="I307" s="6" t="inlineStr">
+      <c r="I307" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -15034,7 +15062,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2027/2028</t>
+          <t>2027/2028, 2025/2026</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15081,7 +15109,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026, 2027/2028</t>
+          <t>2027/2028, 2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">
@@ -15374,215 +15402,215 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B318" s="6" t="inlineStr">
+      <c r="A318" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B318" s="7" t="inlineStr">
         <is>
           <t>A2D2</t>
         </is>
       </c>
-      <c r="C318" s="6" t="inlineStr">
+      <c r="C318" s="7" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D318" s="6" t="inlineStr">
+      <c r="D318" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E318" s="6" t="inlineStr">
+      <c r="E318" s="7" t="inlineStr">
         <is>
           <t>11/07/2026</t>
         </is>
       </c>
-      <c r="F318" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G318" s="6" t="inlineStr"/>
-      <c r="H318" s="6" t="inlineStr">
+      <c r="F318" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G318" s="7" t="inlineStr"/>
+      <c r="H318" s="7" t="inlineStr">
         <is>
           <t>0/40</t>
         </is>
       </c>
-      <c r="I318" s="6" t="inlineStr">
+      <c r="I318" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B319" s="6" t="inlineStr">
+      <c r="A319" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B319" s="7" t="inlineStr">
         <is>
           <t>A2D2</t>
         </is>
       </c>
-      <c r="C319" s="6" t="inlineStr">
+      <c r="C319" s="7" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D319" s="6" t="inlineStr">
+      <c r="D319" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E319" s="6" t="inlineStr">
+      <c r="E319" s="7" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="F319" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G319" s="6" t="inlineStr"/>
-      <c r="H319" s="6" t="inlineStr">
+      <c r="F319" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G319" s="7" t="inlineStr"/>
+      <c r="H319" s="7" t="inlineStr">
         <is>
           <t>0/40</t>
         </is>
       </c>
-      <c r="I319" s="6" t="inlineStr">
+      <c r="I319" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B320" s="6" t="inlineStr">
+      <c r="A320" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B320" s="7" t="inlineStr">
         <is>
           <t>A2D2</t>
         </is>
       </c>
-      <c r="C320" s="6" t="inlineStr">
+      <c r="C320" s="7" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D320" s="6" t="inlineStr">
+      <c r="D320" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E320" s="6" t="inlineStr">
+      <c r="E320" s="7" t="inlineStr">
         <is>
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="F320" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G320" s="6" t="inlineStr"/>
-      <c r="H320" s="6" t="inlineStr">
+      <c r="F320" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G320" s="7" t="inlineStr"/>
+      <c r="H320" s="7" t="inlineStr">
         <is>
           <t>0/40</t>
         </is>
       </c>
-      <c r="I320" s="6" t="inlineStr">
+      <c r="I320" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B321" s="6" t="inlineStr">
+      <c r="A321" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B321" s="7" t="inlineStr">
         <is>
           <t>A2D2</t>
         </is>
       </c>
-      <c r="C321" s="6" t="inlineStr">
+      <c r="C321" s="7" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D321" s="6" t="inlineStr">
+      <c r="D321" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E321" s="6" t="inlineStr">
+      <c r="E321" s="7" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F321" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G321" s="6" t="inlineStr"/>
-      <c r="H321" s="6" t="inlineStr">
+      <c r="F321" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G321" s="7" t="inlineStr"/>
+      <c r="H321" s="7" t="inlineStr">
         <is>
           <t>0/40</t>
         </is>
       </c>
-      <c r="I321" s="6" t="inlineStr">
+      <c r="I321" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B322" s="6" t="inlineStr">
+      <c r="A322" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B322" s="7" t="inlineStr">
         <is>
           <t>A2D2</t>
         </is>
       </c>
-      <c r="C322" s="6" t="inlineStr">
+      <c r="C322" s="7" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D322" s="6" t="inlineStr">
+      <c r="D322" s="7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E322" s="6" t="inlineStr">
+      <c r="E322" s="7" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F322" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G322" s="6" t="inlineStr"/>
-      <c r="H322" s="6" t="inlineStr">
+      <c r="F322" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G322" s="7" t="inlineStr"/>
+      <c r="H322" s="7" t="inlineStr">
         <is>
           <t>0/40</t>
         </is>
       </c>
-      <c r="I322" s="6" t="inlineStr">
+      <c r="I322" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -964,7 +964,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>64.5%</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>78.5%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1478,22 +1478,22 @@
         <v>40</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>8</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>76.6%</t>
         </is>
       </c>
     </row>
@@ -1560,22 +1560,22 @@
         <v>40</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>8</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>82.3%</t>
+          <t>82.5%</t>
         </is>
       </c>
     </row>
@@ -1642,22 +1642,22 @@
         <v>40</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>8</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>80.9%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1724,22 +1724,22 @@
         <v>40</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>8</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>80.4%</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -4728,45 +4728,49 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
         <is>
           <t>A2B1</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C84" s="5" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="D84" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E84" s="5" t="inlineStr">
         <is>
           <t>05/07/2026</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>35/37</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5147,7 +5151,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5194,7 +5198,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5331,7 +5335,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5468,7 +5472,7 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
@@ -5515,7 +5519,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -5562,7 +5566,7 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
@@ -5938,7 +5942,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -6556,45 +6560,49 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
         <is>
           <t>A2B2</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
+      <c r="C124" s="5" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="D124" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E124" s="5" t="inlineStr">
         <is>
           <t>05/07/2026</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>0/36</t>
-        </is>
-      </c>
-      <c r="I124" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="inlineStr">
+        <is>
+          <t>32/36</t>
+        </is>
+      </c>
+      <c r="I124" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6983,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7022,7 +7030,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7159,7 +7167,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7296,7 +7304,7 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
@@ -7343,7 +7351,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -7390,7 +7398,7 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
@@ -7527,7 +7535,7 @@
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -7621,7 +7629,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7762,7 +7770,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -8838,45 +8846,49 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B174" s="2" t="inlineStr">
+      <c r="A174" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B174" s="5" t="inlineStr">
         <is>
           <t>A2C1</t>
         </is>
       </c>
-      <c r="C174" s="2" t="inlineStr">
+      <c r="C174" s="5" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="D174" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E174" s="5" t="inlineStr">
         <is>
           <t>05/07/2026</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I174" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F174" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G174" s="5" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="H174" s="5" t="inlineStr">
+        <is>
+          <t>36/37</t>
+        </is>
+      </c>
+      <c r="I174" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9531,7 +9543,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -10658,45 +10670,49 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B214" s="2" t="inlineStr">
+      <c r="A214" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B214" s="5" t="inlineStr">
         <is>
           <t>A2C2</t>
         </is>
       </c>
-      <c r="C214" s="2" t="inlineStr">
+      <c r="C214" s="5" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D214" s="2" t="inlineStr">
+      <c r="D214" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E214" s="2" t="inlineStr">
+      <c r="E214" s="5" t="inlineStr">
         <is>
           <t>05/07/2026</t>
         </is>
       </c>
-      <c r="F214" s="2" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G214" s="2" t="inlineStr"/>
-      <c r="H214" s="2" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I214" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F214" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G214" s="5" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="H214" s="5" t="inlineStr">
+        <is>
+          <t>17/37</t>
+        </is>
+      </c>
+      <c r="I214" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11351,7 +11367,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -12467,7 +12483,7 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
@@ -12561,7 +12577,7 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr">
@@ -12655,7 +12671,7 @@
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H257" s="5" t="inlineStr">
@@ -12835,7 +12851,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -12882,7 +12898,7 @@
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H262" s="5" t="inlineStr">
@@ -13191,7 +13207,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13285,7 +13301,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2025/2026, 2026/2027</t>
+          <t>2027/2028, 2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -14291,7 +14307,7 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
@@ -14385,7 +14401,7 @@
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H295" s="5" t="inlineStr">
@@ -14479,7 +14495,7 @@
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H297" s="5" t="inlineStr">
@@ -14663,7 +14679,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -14710,7 +14726,7 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
@@ -15027,7 +15043,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15121,7 +15137,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2025/2026, 2026/2027</t>
+          <t>2027/2028, 2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -13301,7 +13301,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026, 2027/2028</t>
+          <t>2025/2026, 2027/2028, 2026/2027</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -15137,7 +15137,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026, 2027/2028</t>
+          <t>2025/2026, 2027/2028, 2026/2027</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1105,7 +1105,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 160715@med.asu.edu.eg</t>
+          <t>160715@med.asu.edu.eg, 2025/2026</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
@@ -11367,7 +11367,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 160715@med.asu.edu.eg</t>
+          <t>160715@med.asu.edu.eg, 2025/2026</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -12483,7 +12483,7 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H257" s="5" t="inlineStr">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H262" s="5" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
@@ -14401,7 +14401,7 @@
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H295" s="5" t="inlineStr">
@@ -14495,7 +14495,7 @@
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H297" s="5" t="inlineStr">
@@ -14679,7 +14679,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
@@ -15043,7 +15043,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1105,7 +1105,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
@@ -7312,7 +7312,7 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr">
@@ -12679,7 +12679,7 @@
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H257" s="5" t="inlineStr">
@@ -12906,7 +12906,7 @@
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H262" s="5" t="inlineStr">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H295" s="5" t="inlineStr">
@@ -14503,7 +14503,7 @@
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H297" s="5" t="inlineStr">
@@ -14734,7 +14734,7 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
@@ -15055,7 +15055,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
@@ -964,7 +964,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>68.2%</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>78.5%</t>
         </is>
       </c>
     </row>
@@ -1318,22 +1318,22 @@
         <v>40</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P15" s="4" t="n">
         <v>8</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>79.1%</t>
         </is>
       </c>
     </row>
@@ -1400,22 +1400,22 @@
         <v>41</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P16" s="4" t="n">
         <v>11</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>79.5%</t>
         </is>
       </c>
     </row>
@@ -1481,10 +1481,10 @@
         <v>29</v>
       </c>
       <c r="P17" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q17" s="4" t="n">
         <v>5</v>
-      </c>
-      <c r="Q17" s="4" t="n">
-        <v>6</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1563,10 +1563,10 @@
         <v>28</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1645,10 +1645,10 @@
         <v>27</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1727,10 +1727,10 @@
         <v>25</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1809,10 +1809,10 @@
         <v>26</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1888,22 +1888,22 @@
         <v>40</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P22" s="4" t="n">
         <v>3</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>67.9%</t>
         </is>
       </c>
     </row>
@@ -2521,45 +2521,49 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>A2A1</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>PHYSICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G35" s="9" t="inlineStr"/>
-      <c r="H35" s="9" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>33/37</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4376,45 +4380,49 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="9" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B76" s="9" t="inlineStr">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>A2A2</t>
         </is>
       </c>
-      <c r="C76" s="9" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>PHYSICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D76" s="9" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E76" s="9" t="inlineStr">
+      <c r="E76" s="5" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F76" s="9" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G76" s="9" t="inlineStr"/>
-      <c r="H76" s="9" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I76" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>32/35</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4881,45 +4889,45 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="9" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B87" s="9" t="inlineStr">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>A2B1</t>
         </is>
       </c>
-      <c r="C87" s="9" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D87" s="9" t="inlineStr">
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E87" s="9" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F87" s="9" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G87" s="9" t="inlineStr"/>
-      <c r="H87" s="9" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I87" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5179,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5218,7 +5226,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5355,7 +5363,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5962,7 +5970,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -6717,45 +6725,45 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="9" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B127" s="9" t="inlineStr">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>A2B2</t>
         </is>
       </c>
-      <c r="C127" s="9" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D127" s="9" t="inlineStr">
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E127" s="9" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F127" s="9" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G127" s="9" t="inlineStr"/>
-      <c r="H127" s="9" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I127" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7007,7 +7015,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7054,7 +7062,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7191,7 +7199,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7559,7 +7567,7 @@
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -7653,7 +7661,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7794,7 +7802,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9007,45 +9015,45 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="9" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B177" s="9" t="inlineStr">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>A2C1</t>
         </is>
       </c>
-      <c r="C177" s="9" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D177" s="9" t="inlineStr">
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E177" s="9" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F177" s="9" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G177" s="9" t="inlineStr"/>
-      <c r="H177" s="9" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I177" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9571,7 +9579,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9853,7 +9861,7 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>160715@med.asu.edu.eg, 2025/2026</t>
+          <t>2025/2026, 160715@med.asu.edu.eg</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
@@ -10831,45 +10839,45 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="9" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B217" s="9" t="inlineStr">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
         <is>
           <t>A2C2</t>
         </is>
       </c>
-      <c r="C217" s="9" t="inlineStr">
+      <c r="C217" s="2" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D217" s="9" t="inlineStr">
+      <c r="D217" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E217" s="9" t="inlineStr">
+      <c r="E217" s="2" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F217" s="9" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G217" s="9" t="inlineStr"/>
-      <c r="H217" s="9" t="inlineStr">
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I217" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11395,7 +11403,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11677,7 +11685,7 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>160715@med.asu.edu.eg, 2025/2026</t>
+          <t>2025/2026, 160715@med.asu.edu.eg</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -12879,7 +12887,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -13282,7 +13290,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2025/2026</t>
+          <t>2025/2026, 2027/2028</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13329,7 +13337,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2027/2028, 2025/2026</t>
+          <t>2025/2026, 2027/2028, 2026/2027</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -13794,45 +13802,45 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="9" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B282" s="9" t="inlineStr">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
         <is>
           <t>A2D1</t>
         </is>
       </c>
-      <c r="C282" s="9" t="inlineStr">
+      <c r="C282" s="2" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D282" s="9" t="inlineStr">
+      <c r="D282" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E282" s="9" t="inlineStr">
+      <c r="E282" s="2" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F282" s="9" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G282" s="9" t="inlineStr"/>
-      <c r="H282" s="9" t="inlineStr">
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr"/>
+      <c r="H282" s="2" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I282" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I282" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14707,7 +14715,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -14957,45 +14965,49 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="9" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B307" s="9" t="inlineStr">
+      <c r="A307" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B307" s="5" t="inlineStr">
         <is>
           <t>A2D2</t>
         </is>
       </c>
-      <c r="C307" s="9" t="inlineStr">
+      <c r="C307" s="5" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D307" s="9" t="inlineStr">
+      <c r="D307" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E307" s="9" t="inlineStr">
+      <c r="E307" s="5" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F307" s="9" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G307" s="9" t="inlineStr"/>
-      <c r="H307" s="9" t="inlineStr">
-        <is>
-          <t>0/40</t>
-        </is>
-      </c>
-      <c r="I307" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F307" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G307" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H307" s="5" t="inlineStr">
+        <is>
+          <t>10/40</t>
+        </is>
+      </c>
+      <c r="I307" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -15126,7 +15138,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2025/2026</t>
+          <t>2025/2026, 2027/2028</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15173,7 +15185,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2027/2028, 2025/2026</t>
+          <t>2025/2026, 2027/2028, 2026/2027</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
@@ -964,7 +964,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.5%</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>78.5%</t>
+          <t>78.3%</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1642,22 +1642,22 @@
         <v>40</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>5</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>79.4%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -10158,45 +10158,49 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B202" s="2" t="inlineStr">
+      <c r="A202" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B202" s="5" t="inlineStr">
         <is>
           <t>A2C1</t>
         </is>
       </c>
-      <c r="C202" s="2" t="inlineStr">
+      <c r="C202" s="5" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="D202" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="E202" s="5" t="inlineStr">
         <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="F202" s="2" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G202" s="2" t="inlineStr"/>
-      <c r="H202" s="2" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I202" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F202" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G202" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H202" s="5" t="inlineStr">
+        <is>
+          <t>13/37</t>
+        </is>
+      </c>
+      <c r="I202" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11403,7 +11407,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -12519,7 +12523,7 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
@@ -12613,7 +12617,7 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr">
@@ -12707,7 +12711,7 @@
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H257" s="5" t="inlineStr">
@@ -12887,7 +12891,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -12934,7 +12938,7 @@
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H262" s="5" t="inlineStr">
@@ -13243,7 +13247,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13290,7 +13294,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2027/2028</t>
+          <t>2027/2028, 2025/2026</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13337,7 +13341,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2027/2028, 2026/2027</t>
+          <t>2026/2027, 2027/2028, 2025/2026</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -14343,7 +14347,7 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
@@ -14437,7 +14441,7 @@
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H295" s="5" t="inlineStr">
@@ -14531,7 +14535,7 @@
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H297" s="5" t="inlineStr">
@@ -14715,7 +14719,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -14762,7 +14766,7 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
@@ -15091,7 +15095,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15138,7 +15142,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2027/2028</t>
+          <t>2027/2028, 2025/2026</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15185,7 +15189,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2027/2028, 2026/2027</t>
+          <t>2026/2027, 2027/2028, 2025/2026</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -9869,7 +9869,7 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 160715@med.asu.edu.eg</t>
+          <t>160715@med.asu.edu.eg, 2025/2026</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 160715@med.asu.edu.eg</t>
+          <t>160715@med.asu.edu.eg, 2025/2026</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2025/2026</t>
+          <t>2025/2026, 2027/2028</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2027/2028, 2025/2026</t>
+          <t>2026/2027, 2025/2026, 2027/2028</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -15150,7 +15150,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2025/2026</t>
+          <t>2025/2026, 2027/2028</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15197,7 +15197,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2027/2028, 2025/2026</t>
+          <t>2026/2027, 2025/2026, 2027/2028</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9">
@@ -964,7 +964,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>70.4%</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>77.6%</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1318,22 +1318,22 @@
         <v>40</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P15" s="4" t="n">
         <v>8</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>79.1%</t>
+          <t>77.4%</t>
         </is>
       </c>
     </row>
@@ -1400,22 +1400,22 @@
         <v>41</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P16" s="4" t="n">
         <v>11</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>78.5%</t>
         </is>
       </c>
     </row>
@@ -1481,10 +1481,10 @@
         <v>29</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1563,10 +1563,10 @@
         <v>28</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1642,22 +1642,22 @@
         <v>40</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P19" s="4" t="n">
         <v>5</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>77.2%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1724,22 +1724,22 @@
         <v>40</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P20" s="4" t="n">
         <v>10</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>79.3%</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -1809,10 +1809,10 @@
         <v>26</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1891,10 +1891,10 @@
         <v>32</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2349,45 +2349,49 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>A2A1</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>11/07/2026</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G31" s="9" t="inlineStr"/>
-      <c r="H31" s="9" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>12/37</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3375,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3731,7 +3735,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -3778,7 +3782,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -4208,45 +4212,49 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="9" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="inlineStr">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
         <is>
           <t>A2A2</t>
         </is>
       </c>
-      <c r="C72" s="9" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D72" s="9" t="inlineStr">
+      <c r="D72" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E72" s="9" t="inlineStr">
+      <c r="E72" s="5" t="inlineStr">
         <is>
           <t>11/07/2026</t>
         </is>
       </c>
-      <c r="F72" s="9" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G72" s="9" t="inlineStr"/>
-      <c r="H72" s="9" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I72" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>18/35</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4932,45 +4940,45 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="9" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B88" s="9" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>A2B1</t>
         </is>
       </c>
-      <c r="C88" s="9" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D88" s="9" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E88" s="9" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>11/07/2026</t>
         </is>
       </c>
-      <c r="F88" s="9" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G88" s="9" t="inlineStr"/>
-      <c r="H88" s="9" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I88" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5187,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5226,7 +5234,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5363,7 +5371,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5500,7 +5508,7 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
@@ -5547,7 +5555,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -5594,7 +5602,7 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
@@ -5970,7 +5978,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -6768,45 +6776,45 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="9" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B128" s="9" t="inlineStr">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>A2B2</t>
         </is>
       </c>
-      <c r="C128" s="9" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D128" s="9" t="inlineStr">
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E128" s="9" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>11/07/2026</t>
         </is>
       </c>
-      <c r="F128" s="9" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G128" s="9" t="inlineStr"/>
-      <c r="H128" s="9" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I128" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7023,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7062,7 +7070,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7199,7 +7207,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7336,7 +7344,7 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
@@ -7383,7 +7391,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -7430,7 +7438,7 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
@@ -7567,7 +7575,7 @@
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -7661,7 +7669,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7802,7 +7810,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9066,45 +9074,49 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="9" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B178" s="9" t="inlineStr">
+      <c r="A178" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B178" s="5" t="inlineStr">
         <is>
           <t>A2C1</t>
         </is>
       </c>
-      <c r="C178" s="9" t="inlineStr">
+      <c r="C178" s="5" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D178" s="9" t="inlineStr">
+      <c r="D178" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E178" s="9" t="inlineStr">
+      <c r="E178" s="5" t="inlineStr">
         <is>
           <t>11/07/2026</t>
         </is>
       </c>
-      <c r="F178" s="9" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G178" s="9" t="inlineStr"/>
-      <c r="H178" s="9" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I178" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F178" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G178" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H178" s="5" t="inlineStr">
+        <is>
+          <t>26/37</t>
+        </is>
+      </c>
+      <c r="I178" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9587,7 +9599,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9869,7 +9881,7 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>160715@med.asu.edu.eg, 2025/2026</t>
+          <t>2025/2026, 160715@med.asu.edu.eg</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
@@ -10894,45 +10906,49 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="9" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B218" s="9" t="inlineStr">
+      <c r="A218" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B218" s="5" t="inlineStr">
         <is>
           <t>A2C2</t>
         </is>
       </c>
-      <c r="C218" s="9" t="inlineStr">
+      <c r="C218" s="5" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D218" s="9" t="inlineStr">
+      <c r="D218" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E218" s="9" t="inlineStr">
+      <c r="E218" s="5" t="inlineStr">
         <is>
           <t>11/07/2026</t>
         </is>
       </c>
-      <c r="F218" s="9" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G218" s="9" t="inlineStr"/>
-      <c r="H218" s="9" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I218" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F218" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G218" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H218" s="5" t="inlineStr">
+        <is>
+          <t>19/37</t>
+        </is>
+      </c>
+      <c r="I218" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11415,7 +11431,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11697,7 +11713,7 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>160715@med.asu.edu.eg, 2025/2026</t>
+          <t>2025/2026, 160715@med.asu.edu.eg</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -12531,7 +12547,7 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
@@ -12625,7 +12641,7 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr">
@@ -12719,7 +12735,7 @@
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H257" s="5" t="inlineStr">
@@ -12899,7 +12915,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -12946,7 +12962,7 @@
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H262" s="5" t="inlineStr">
@@ -12961,45 +12977,45 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="9" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B263" s="9" t="inlineStr">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
         <is>
           <t>A2D1</t>
         </is>
       </c>
-      <c r="C263" s="9" t="inlineStr">
+      <c r="C263" s="2" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D263" s="9" t="inlineStr">
+      <c r="D263" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E263" s="9" t="inlineStr">
+      <c r="E263" s="2" t="inlineStr">
         <is>
           <t>11/07/2026</t>
         </is>
       </c>
-      <c r="F263" s="9" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G263" s="9" t="inlineStr"/>
-      <c r="H263" s="9" t="inlineStr">
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr"/>
+      <c r="H263" s="2" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I263" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I263" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13255,7 +13271,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13302,7 +13318,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2027/2028</t>
+          <t>2027/2028, 2025/2026</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13349,7 +13365,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026, 2027/2028</t>
+          <t>2027/2028, 2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -14355,7 +14371,7 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
@@ -14449,7 +14465,7 @@
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H295" s="5" t="inlineStr">
@@ -14543,7 +14559,7 @@
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H297" s="5" t="inlineStr">
@@ -14727,7 +14743,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -14774,7 +14790,7 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
@@ -15103,7 +15119,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15150,7 +15166,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2027/2028</t>
+          <t>2027/2028, 2025/2026</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15197,7 +15213,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026, 2027/2028</t>
+          <t>2027/2028, 2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">
@@ -15490,45 +15506,45 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="9" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B318" s="9" t="inlineStr">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
         <is>
           <t>A2D2</t>
         </is>
       </c>
-      <c r="C318" s="9" t="inlineStr">
+      <c r="C318" s="2" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D318" s="9" t="inlineStr">
+      <c r="D318" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E318" s="9" t="inlineStr">
+      <c r="E318" s="2" t="inlineStr">
         <is>
           <t>11/07/2026</t>
         </is>
       </c>
-      <c r="F318" s="9" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G318" s="9" t="inlineStr"/>
-      <c r="H318" s="9" t="inlineStr">
+      <c r="F318" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G318" s="2" t="inlineStr"/>
+      <c r="H318" s="2" t="inlineStr">
         <is>
           <t>0/40</t>
         </is>
       </c>
-      <c r="I318" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I318" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1105,7 +1105,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>160715@med.asu.edu.eg, 2025/2026</t>
+          <t>2025/2026, 160715@med.asu.edu.eg</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11721,7 +11721,7 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>160715@med.asu.edu.eg, 2025/2026</t>
+          <t>2025/2026, 160715@med.asu.edu.eg</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -12555,7 +12555,7 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
@@ -12649,7 +12649,7 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr">
@@ -12743,7 +12743,7 @@
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H257" s="5" t="inlineStr">
@@ -12970,7 +12970,7 @@
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H262" s="5" t="inlineStr">
@@ -13283,7 +13283,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -14383,7 +14383,7 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H295" s="5" t="inlineStr">
@@ -14571,7 +14571,7 @@
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H297" s="5" t="inlineStr">
@@ -14802,7 +14802,7 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
@@ -15131,7 +15131,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -9909,7 +9909,7 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>160715@med.asu.edu.eg, 2025/2026</t>
+          <t>2025/2026, 160715@med.asu.edu.eg</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
@@ -11745,7 +11745,7 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>160715@med.asu.edu.eg, 2025/2026</t>
+          <t>2025/2026, 160715@med.asu.edu.eg</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -13358,7 +13358,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2027/2028</t>
+          <t>2027/2028, 2025/2026</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027, 2027/2028</t>
+          <t>2027/2028, 2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2027/2028</t>
+          <t>2027/2028, 2025/2026</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15253,7 +15253,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027, 2027/2028</t>
+          <t>2027/2028, 2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1105,7 +1105,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -12611,7 +12611,7 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
@@ -12705,7 +12705,7 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr">
@@ -12799,7 +12799,7 @@
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H257" s="5" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H262" s="5" t="inlineStr">
@@ -13347,7 +13347,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2026/2027, 2025/2026</t>
+          <t>2026/2027, 2027/2028, 2025/2026</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -14447,7 +14447,7 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H295" s="5" t="inlineStr">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H297" s="5" t="inlineStr">
@@ -14866,7 +14866,7 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
@@ -15195,7 +15195,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15289,7 +15289,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2026/2027, 2025/2026</t>
+          <t>2026/2027, 2027/2028, 2025/2026</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -9957,7 +9957,7 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>160715@med.asu.edu.eg, 2025/2026</t>
+          <t>2025/2026, 160715@med.asu.edu.eg</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>160715@med.asu.edu.eg, 2025/2026</t>
+          <t>2025/2026, 160715@med.asu.edu.eg</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2026/2027, 2025/2026</t>
+          <t>2026/2027, 2027/2028, 2025/2026</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -15313,7 +15313,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2026/2027, 2025/2026</t>
+          <t>2026/2027, 2027/2028, 2025/2026</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -81,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -103,9 +103,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -802,7 +799,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7">
@@ -853,7 +850,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8">
@@ -908,7 +905,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -964,7 +961,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>78.8%</t>
+          <t>79.4%</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1018,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>77.9%</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1318,17 +1315,17 @@
         <v>40</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P15" s="4" t="n">
         <v>8</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
@@ -1400,22 +1397,22 @@
         <v>41</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P16" s="4" t="n">
         <v>11</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>73.2%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>79.4%</t>
         </is>
       </c>
     </row>
@@ -1481,10 +1478,10 @@
         <v>34</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1563,10 +1560,10 @@
         <v>33</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1645,10 +1642,10 @@
         <v>34</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1694,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1727,10 +1724,10 @@
         <v>29</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1776,7 +1773,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -1809,10 +1806,10 @@
         <v>29</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1891,10 +1888,10 @@
         <v>34</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2584,45 +2581,49 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>A2A1</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>PHYSICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G36" s="9" t="inlineStr"/>
-      <c r="H36" s="9" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>28/37</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3747,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -3794,7 +3795,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -4459,45 +4460,49 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="9" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B77" s="9" t="inlineStr">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
         <is>
           <t>A2A2</t>
         </is>
       </c>
-      <c r="C77" s="9" t="inlineStr">
+      <c r="C77" s="5" t="inlineStr">
         <is>
           <t>PHYSICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D77" s="9" t="inlineStr">
+      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E77" s="9" t="inlineStr">
+      <c r="E77" s="5" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F77" s="9" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G77" s="9" t="inlineStr"/>
-      <c r="H77" s="9" t="inlineStr">
-        <is>
-          <t>0/35</t>
-        </is>
-      </c>
-      <c r="I77" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>35/35</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5156,45 +5161,45 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="9" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B92" s="9" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>A2B1</t>
         </is>
       </c>
-      <c r="C92" s="9" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D92" s="9" t="inlineStr">
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E92" s="9" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F92" s="9" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G92" s="9" t="inlineStr"/>
-      <c r="H92" s="9" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I92" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5231,7 +5236,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5278,7 +5283,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5415,7 +5420,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5552,7 +5557,7 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
@@ -5599,7 +5604,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -5646,7 +5651,7 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
@@ -6022,7 +6027,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7012,45 +7017,45 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="9" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B132" s="9" t="inlineStr">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>A2B2</t>
         </is>
       </c>
-      <c r="C132" s="9" t="inlineStr">
+      <c r="C132" s="2" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D132" s="9" t="inlineStr">
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E132" s="9" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F132" s="9" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G132" s="9" t="inlineStr"/>
-      <c r="H132" s="9" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I132" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7092,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7134,7 +7139,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7271,7 +7276,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7408,7 +7413,7 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
@@ -7455,7 +7460,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -7502,7 +7507,7 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
@@ -7639,7 +7644,7 @@
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -7733,7 +7738,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7874,7 +7879,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9170,7 +9175,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9264,7 +9269,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -9326,45 +9331,45 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="9" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B182" s="9" t="inlineStr">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>A2C1</t>
         </is>
       </c>
-      <c r="C182" s="9" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D182" s="9" t="inlineStr">
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E182" s="9" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F182" s="9" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G182" s="9" t="inlineStr"/>
-      <c r="H182" s="9" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I182" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9680,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9957,7 +9962,7 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 160715@med.asu.edu.eg</t>
+          <t>160715@med.asu.edu.eg, 2025/2026</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
@@ -11014,7 +11019,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11108,7 +11113,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -11170,45 +11175,45 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="9" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B222" s="9" t="inlineStr">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
         <is>
           <t>A2C2</t>
         </is>
       </c>
-      <c r="C222" s="9" t="inlineStr">
+      <c r="C222" s="2" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D222" s="9" t="inlineStr">
+      <c r="D222" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E222" s="9" t="inlineStr">
+      <c r="E222" s="2" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F222" s="9" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G222" s="9" t="inlineStr"/>
-      <c r="H222" s="9" t="inlineStr">
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr"/>
+      <c r="H222" s="2" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I222" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11519,7 +11524,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11801,7 +11806,7 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 160715@med.asu.edu.eg</t>
+          <t>160715@med.asu.edu.eg, 2025/2026</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -12635,7 +12640,7 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
@@ -12729,7 +12734,7 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr">
@@ -12823,7 +12828,7 @@
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H257" s="5" t="inlineStr">
@@ -13003,7 +13008,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -13050,7 +13055,7 @@
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H262" s="5" t="inlineStr">
@@ -13249,45 +13254,45 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="9" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B267" s="9" t="inlineStr">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
         <is>
           <t>A2D1</t>
         </is>
       </c>
-      <c r="C267" s="9" t="inlineStr">
+      <c r="C267" s="2" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D267" s="9" t="inlineStr">
+      <c r="D267" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E267" s="9" t="inlineStr">
+      <c r="E267" s="2" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F267" s="9" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G267" s="9" t="inlineStr"/>
-      <c r="H267" s="9" t="inlineStr">
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr"/>
+      <c r="H267" s="2" t="inlineStr">
         <is>
           <t>0/34</t>
         </is>
       </c>
-      <c r="I267" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13376,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13418,7 +13423,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2025/2026</t>
+          <t>2025/2026, 2027/2028</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13465,7 +13470,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2025/2026, 2026/2027</t>
+          <t>2025/2026, 2026/2027, 2027/2028</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -14471,7 +14476,7 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
@@ -14565,7 +14570,7 @@
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H295" s="5" t="inlineStr">
@@ -14659,7 +14664,7 @@
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H297" s="5" t="inlineStr">
@@ -14843,7 +14848,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -14890,7 +14895,7 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
@@ -15219,7 +15224,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15266,7 +15271,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2025/2026</t>
+          <t>2025/2026, 2027/2028</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15313,7 +15318,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2025/2026, 2026/2027</t>
+          <t>2025/2026, 2026/2027, 2027/2028</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">
@@ -15786,45 +15791,45 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="9" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B322" s="9" t="inlineStr">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
         <is>
           <t>A2D2</t>
         </is>
       </c>
-      <c r="C322" s="9" t="inlineStr">
+      <c r="C322" s="2" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D322" s="9" t="inlineStr">
+      <c r="D322" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E322" s="9" t="inlineStr">
+      <c r="E322" s="2" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F322" s="9" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G322" s="9" t="inlineStr"/>
-      <c r="H322" s="9" t="inlineStr">
+      <c r="F322" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G322" s="2" t="inlineStr"/>
+      <c r="H322" s="2" t="inlineStr">
         <is>
           <t>0/40</t>
         </is>
       </c>
-      <c r="I322" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I322" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
@@ -6027,7 +6027,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9175,7 +9175,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -9684,7 +9684,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>160715@med.asu.edu.eg, 2025/2026</t>
+          <t>2025/2026, 160715@med.asu.edu.eg</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -11532,7 +11532,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>160715@med.asu.edu.eg, 2025/2026</t>
+          <t>2025/2026, 160715@med.asu.edu.eg</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
@@ -12742,7 +12742,7 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H257" s="5" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -13063,7 +13063,7 @@
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H262" s="5" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13435,7 +13435,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2025/2026</t>
+          <t>2025/2026, 2027/2028</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13482,7 +13482,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027, 2027/2028</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
@@ -14582,7 +14582,7 @@
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H295" s="5" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H297" s="5" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -14907,7 +14907,7 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
@@ -15236,7 +15236,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15283,7 +15283,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2025/2026</t>
+          <t>2025/2026, 2027/2028</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15330,7 +15330,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027, 2027/2028</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -9966,7 +9966,7 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>160715@med.asu.edu.eg, 2025/2026</t>
+          <t>2025/2026, 160715@med.asu.edu.eg</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
@@ -11822,7 +11822,7 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>160715@med.asu.edu.eg, 2025/2026</t>
+          <t>2025/2026, 160715@med.asu.edu.eg</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2025/2026</t>
+          <t>2025/2026, 2027/2028</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13490,7 +13490,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2025/2026, 2026/2027</t>
+          <t>2025/2026, 2026/2027, 2027/2028</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -15291,7 +15291,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2025/2026</t>
+          <t>2025/2026, 2027/2028</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15338,7 +15338,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2025/2026, 2026/2027</t>
+          <t>2025/2026, 2026/2027, 2027/2028</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 160715@med.asu.edu.eg</t>
+          <t>160715@med.asu.edu.eg, 2025/2026</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 160715@med.asu.edu.eg</t>
+          <t>160715@med.asu.edu.eg, 2025/2026</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2026/2027, 2025/2026</t>
+          <t>2027/2028, 2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -14876,7 +14876,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -15346,7 +15346,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2026/2027, 2025/2026</t>
+          <t>2027/2028, 2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2025/2026</t>
+          <t>2025/2026, 2027/2028</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2026/2027, 2025/2026</t>
+          <t>2026/2027, 2025/2026, 2027/2028</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2025/2026</t>
+          <t>2025/2026, 2027/2028</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15346,7 +15346,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2026/2027, 2025/2026</t>
+          <t>2026/2027, 2025/2026, 2027/2028</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>160715@med.asu.edu.eg, 2025/2026</t>
+          <t>2025/2026, 160715@med.asu.edu.eg</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>160715@med.asu.edu.eg, 2025/2026</t>
+          <t>2025/2026, 160715@med.asu.edu.eg</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -12664,7 +12664,7 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr">
@@ -12852,7 +12852,7 @@
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H257" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H262" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2027/2028</t>
+          <t>2027/2028, 2025/2026</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2027/2028, 2026/2027</t>
+          <t>2026/2027, 2027/2028, 2025/2026</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
@@ -14598,7 +14598,7 @@
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H295" s="5" t="inlineStr">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H297" s="5" t="inlineStr">
@@ -14876,7 +14876,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
@@ -15252,7 +15252,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2027/2028</t>
+          <t>2027/2028, 2025/2026</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15346,7 +15346,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2027/2028, 2026/2027</t>
+          <t>2026/2027, 2027/2028, 2025/2026</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 160715@med.asu.edu.eg</t>
+          <t>160715@med.asu.edu.eg, 2025/2026</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 160715@med.asu.edu.eg</t>
+          <t>160715@med.asu.edu.eg, 2025/2026</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -12664,7 +12664,7 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr">
@@ -12852,7 +12852,7 @@
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H257" s="5" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H262" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2025/2026</t>
+          <t>2025/2026, 2027/2028</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026, 2027/2028</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
@@ -14598,7 +14598,7 @@
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H295" s="5" t="inlineStr">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H297" s="5" t="inlineStr">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
@@ -15252,7 +15252,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2025/2026</t>
+          <t>2025/2026, 2027/2028</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15346,7 +15346,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026, 2027/2028</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 160715@med.asu.edu.eg</t>
+          <t>160715@med.asu.edu.eg, 2025/2026</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 160715@med.asu.edu.eg</t>
+          <t>160715@med.asu.edu.eg, 2025/2026</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -12664,7 +12664,7 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr">
@@ -12852,7 +12852,7 @@
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H257" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H262" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026, 2027/2028</t>
+          <t>2025/2026, 2026/2027, 2027/2028</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
@@ -14598,7 +14598,7 @@
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H295" s="5" t="inlineStr">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H297" s="5" t="inlineStr">
@@ -14876,7 +14876,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
@@ -15252,7 +15252,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15346,7 +15346,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026, 2027/2028</t>
+          <t>2025/2026, 2026/2027, 2027/2028</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>160715@med.asu.edu.eg, 2025/2026</t>
+          <t>2025/2026, 160715@med.asu.edu.eg</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>160715@med.asu.edu.eg, 2025/2026</t>
+          <t>2025/2026, 160715@med.asu.edu.eg</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -12664,7 +12664,7 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr">
@@ -12852,7 +12852,7 @@
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H257" s="5" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H262" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2027/2028, 2025/2026</t>
+          <t>2027/2028, 2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
@@ -14598,7 +14598,7 @@
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H295" s="5" t="inlineStr">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H297" s="5" t="inlineStr">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
@@ -15252,7 +15252,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15346,7 +15346,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2027/2028, 2025/2026</t>
+          <t>2027/2028, 2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -725,7 +725,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Taqwa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Taqwa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Taqwa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Taqwa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Sohairhassan</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Sohairhassan</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Dr. Tasneem El-Sayed</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Dr. Tasneem El-Sayed</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Dr. Tasneem El-Sayed</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Dr. Tasneem El-Sayed</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Taqwa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>Sohairhassan</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H76" s="5" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>Sohairhassan</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>Dr. Tasneem El-Sayed</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H78" s="5" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Tasneem El-Sayed</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Tasneem El-Sayed</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Tasneem El-Sayed</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>Dr. Tasneem El-Sayed</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H82" s="5" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H84" s="5" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H86" s="5" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H90" s="5" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H91" s="5" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H92" s="5" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H96" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>Taqwa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>Taqwa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H104" s="5" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>Taqwa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H106" s="5" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H108" s="5" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H112" s="5" t="inlineStr">
@@ -6172,7 +6172,7 @@
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H113" s="5" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H114" s="5" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>Sohairhassan</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H116" s="5" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>Sohairhassan</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>Dr. Tasneem El-Sayed</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H120" s="5" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>Dr. Tasneem El-Sayed</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>Dr. Tasneem El-Sayed</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H122" s="5" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H126" s="5" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H132" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H144" s="5" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>Dou7a</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>Nephrology Resident</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H146" s="5" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="G148" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H148" s="5" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="G152" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H152" s="5" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H154" s="5" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="G156" s="5" t="inlineStr">
         <is>
-          <t>Sohairhassan</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H156" s="5" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>Sohairhassan</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>Dr. Tasneem El-Sayed</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H158" s="5" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>Dr. Tasneem El-Sayed</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="G160" s="5" t="inlineStr">
         <is>
-          <t>Dr. Tasneem El-Sayed</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H160" s="5" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>Dr. Tasneem El-Sayed</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="G164" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H164" s="5" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H167" s="5" t="inlineStr">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="G168" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H168" s="5" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H169" s="5" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H170" s="5" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H175" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H181" s="5" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="G182" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H182" s="5" t="inlineStr">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="G183" s="5" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H183" s="5" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H185" s="5" t="inlineStr">
@@ -9555,7 +9555,7 @@
       </c>
       <c r="G186" s="5" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H186" s="5" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="G187" s="5" t="inlineStr">
         <is>
-          <t>Nephrology Resident</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H187" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="G190" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H190" s="5" t="inlineStr">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="G191" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H191" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="G193" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H193" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh</t>
+          <t>2025/2026, 160715@med.asu.edu.eg</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
@@ -10021,7 +10021,7 @@
       </c>
       <c r="G196" s="5" t="inlineStr">
         <is>
-          <t>Sohairhassan</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H196" s="5" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="G197" s="5" t="inlineStr">
         <is>
-          <t>Sohairhassan</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H197" s="5" t="inlineStr">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="G198" s="5" t="inlineStr">
         <is>
-          <t>Dr. Tasneem El-Sayed</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H198" s="5" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Dr. Tasneem El-Sayed</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="G200" s="5" t="inlineStr">
         <is>
-          <t>Dr. Tasneem El-Sayed</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H200" s="5" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="G201" s="5" t="inlineStr">
         <is>
-          <t>Dr. Tasneem El-Sayed</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H201" s="5" t="inlineStr">
@@ -10303,7 +10303,7 @@
       </c>
       <c r="G202" s="5" t="inlineStr">
         <is>
-          <t>Dr. Tasneem El-Sayed</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H202" s="5" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="G203" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H203" s="5" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="G204" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H204" s="5" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="G205" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H205" s="5" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="G207" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H207" s="5" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="G208" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H208" s="5" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="G209" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H209" s="5" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="G210" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H210" s="5" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="G221" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H221" s="5" t="inlineStr">
@@ -11227,7 +11227,7 @@
       </c>
       <c r="G222" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H222" s="5" t="inlineStr">
@@ -11317,7 +11317,7 @@
       </c>
       <c r="G224" s="5" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H224" s="5" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="G225" s="5" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H225" s="5" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="G226" s="5" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H226" s="5" t="inlineStr">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="G227" s="5" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H227" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11595,7 +11595,7 @@
       </c>
       <c r="G230" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H230" s="5" t="inlineStr">
@@ -11642,7 +11642,7 @@
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H231" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -11736,7 +11736,7 @@
       </c>
       <c r="G233" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H233" s="5" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh</t>
+          <t>2025/2026, 160715@med.asu.edu.eg</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="G236" s="5" t="inlineStr">
         <is>
-          <t>Sohairhassan</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H236" s="5" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>Sohairhassan</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H237" s="5" t="inlineStr">
@@ -11971,7 +11971,7 @@
       </c>
       <c r="G238" s="5" t="inlineStr">
         <is>
-          <t>Dr. Tasneem El-Sayed</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H238" s="5" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="G241" s="5" t="inlineStr">
         <is>
-          <t>Dr. Tasneem El-Sayed</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H241" s="5" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="G242" s="5" t="inlineStr">
         <is>
-          <t>Dr. Tasneem El-Sayed</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H242" s="5" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="G243" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H243" s="5" t="inlineStr">
@@ -12245,7 +12245,7 @@
       </c>
       <c r="G244" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H244" s="5" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H245" s="5" t="inlineStr">
@@ -12339,7 +12339,7 @@
       </c>
       <c r="G246" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H246" s="5" t="inlineStr">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="G247" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H247" s="5" t="inlineStr">
@@ -12433,7 +12433,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H249" s="5" t="inlineStr">
@@ -12527,7 +12527,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H251" s="5" t="inlineStr">
@@ -12664,7 +12664,7 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
@@ -12711,7 +12711,7 @@
       </c>
       <c r="G254" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H254" s="5" t="inlineStr">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr">
@@ -12805,7 +12805,7 @@
       </c>
       <c r="G256" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H256" s="5" t="inlineStr">
@@ -12852,7 +12852,7 @@
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H257" s="5" t="inlineStr">
@@ -12985,7 +12985,7 @@
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H260" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H262" s="5" t="inlineStr">
@@ -13126,7 +13126,7 @@
       </c>
       <c r="G263" s="5" t="inlineStr">
         <is>
-          <t>Taqwa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H263" s="5" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="G264" s="5" t="inlineStr">
         <is>
-          <t>Taqwa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H264" s="5" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="G265" s="5" t="inlineStr">
         <is>
-          <t>Taqwa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H265" s="5" t="inlineStr">
@@ -13310,7 +13310,7 @@
       </c>
       <c r="G267" s="5" t="inlineStr">
         <is>
-          <t>Taqwa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H267" s="5" t="inlineStr">
@@ -13357,7 +13357,7 @@
       </c>
       <c r="G268" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H268" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>2025/2026, 2027/2028</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>2025/2026, 2027/2028, 2026/2027</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -13588,7 +13588,7 @@
       </c>
       <c r="G273" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H273" s="5" t="inlineStr">
@@ -13635,7 +13635,7 @@
       </c>
       <c r="G274" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H274" s="5" t="inlineStr">
@@ -13682,7 +13682,7 @@
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H275" s="5" t="inlineStr">
@@ -13729,7 +13729,7 @@
       </c>
       <c r="G276" s="5" t="inlineStr">
         <is>
-          <t>Sohairhassan</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H276" s="5" t="inlineStr">
@@ -13776,7 +13776,7 @@
       </c>
       <c r="G277" s="5" t="inlineStr">
         <is>
-          <t>Sohairhassan</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H277" s="5" t="inlineStr">
@@ -14038,7 +14038,7 @@
       </c>
       <c r="G283" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H283" s="5" t="inlineStr">
@@ -14085,7 +14085,7 @@
       </c>
       <c r="G284" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H284" s="5" t="inlineStr">
@@ -14132,7 +14132,7 @@
       </c>
       <c r="G285" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H285" s="5" t="inlineStr">
@@ -14179,7 +14179,7 @@
       </c>
       <c r="G286" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H286" s="5" t="inlineStr">
@@ -14226,7 +14226,7 @@
       </c>
       <c r="G287" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H287" s="5" t="inlineStr">
@@ -14273,7 +14273,7 @@
       </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H288" s="5" t="inlineStr">
@@ -14320,7 +14320,7 @@
       </c>
       <c r="G289" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H289" s="5" t="inlineStr">
@@ -14367,7 +14367,7 @@
       </c>
       <c r="G290" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H290" s="5" t="inlineStr">
@@ -14414,7 +14414,7 @@
       </c>
       <c r="G291" s="5" t="inlineStr">
         <is>
-          <t>Mona Hazaa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H291" s="5" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
@@ -14551,7 +14551,7 @@
       </c>
       <c r="G294" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H294" s="5" t="inlineStr">
@@ -14598,7 +14598,7 @@
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H295" s="5" t="inlineStr">
@@ -14645,7 +14645,7 @@
       </c>
       <c r="G296" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H296" s="5" t="inlineStr">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H297" s="5" t="inlineStr">
@@ -14739,7 +14739,7 @@
       </c>
       <c r="G298" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H298" s="5" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="G300" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H300" s="5" t="inlineStr">
@@ -14876,7 +14876,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
@@ -14970,7 +14970,7 @@
       </c>
       <c r="G303" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H303" s="5" t="inlineStr">
@@ -15017,7 +15017,7 @@
       </c>
       <c r="G304" s="5" t="inlineStr">
         <is>
-          <t>Taqwa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H304" s="5" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="G305" s="5" t="inlineStr">
         <is>
-          <t>Taqwa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H305" s="5" t="inlineStr">
@@ -15111,7 +15111,7 @@
       </c>
       <c r="G306" s="5" t="inlineStr">
         <is>
-          <t>Taqwa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H306" s="5" t="inlineStr">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="G307" s="5" t="inlineStr">
         <is>
-          <t>Taqwa</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H307" s="5" t="inlineStr">
@@ -15205,7 +15205,7 @@
       </c>
       <c r="G308" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H308" s="5" t="inlineStr">
@@ -15252,7 +15252,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>2025/2026, 2027/2028</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15346,7 +15346,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>2025/2026, 2027/2028, 2026/2027</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">
@@ -15436,7 +15436,7 @@
       </c>
       <c r="G313" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="H313" s="5" t="inlineStr">
@@ -15483,7 +15483,7 @@
       </c>
       <c r="G314" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H314" s="5" t="inlineStr">
@@ -15530,7 +15530,7 @@
       </c>
       <c r="G315" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H315" s="5" t="inlineStr">
@@ -15577,7 +15577,7 @@
       </c>
       <c r="G316" s="5" t="inlineStr">
         <is>
-          <t>Sohairhassan</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H316" s="5" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="G317" s="5" t="inlineStr">
         <is>
-          <t>Sohairhassan</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H317" s="5" t="inlineStr">
@@ -15671,7 +15671,7 @@
       </c>
       <c r="G318" s="5" t="inlineStr">
         <is>
-          <t>Dr. Tasneem El-Sayed</t>
+          <t>2027/2028</t>
         </is>
       </c>
       <c r="H318" s="5" t="inlineStr">
@@ -15804,7 +15804,7 @@
       </c>
       <c r="G321" s="5" t="inlineStr">
         <is>
-          <t>Dr. Tasneem El-Sayed</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H321" s="5" t="inlineStr">
@@ -15851,7 +15851,7 @@
       </c>
       <c r="G322" s="5" t="inlineStr">
         <is>
-          <t>Dr. Tasneem El-Sayed</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H322" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -725,7 +725,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H76" s="5" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H78" s="5" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H82" s="5" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H84" s="5" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H86" s="5" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H90" s="5" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H91" s="5" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H92" s="5" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Developer, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H96" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H104" s="5" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H106" s="5" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H108" s="5" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H112" s="5" t="inlineStr">
@@ -6172,7 +6172,7 @@
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H113" s="5" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H114" s="5" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H116" s="5" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H120" s="5" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H122" s="5" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H126" s="5" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H132" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Developer, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H144" s="5" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Dou7a</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H146" s="5" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="G148" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H148" s="5" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="G152" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H152" s="5" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H154" s="5" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="G156" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H156" s="5" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H158" s="5" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="G160" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H160" s="5" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="G164" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H164" s="5" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H167" s="5" t="inlineStr">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="G168" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H168" s="5" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H169" s="5" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H170" s="5" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H175" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H181" s="5" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="G182" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H182" s="5" t="inlineStr">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="G183" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H183" s="5" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H185" s="5" t="inlineStr">
@@ -9555,7 +9555,7 @@
       </c>
       <c r="G186" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H186" s="5" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="G187" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H187" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="G190" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H190" s="5" t="inlineStr">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="G191" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H191" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="G193" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H193" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 160715@med.asu.edu.eg</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
@@ -10021,7 +10021,7 @@
       </c>
       <c r="G196" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H196" s="5" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="G197" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H197" s="5" t="inlineStr">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="G198" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H198" s="5" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="G200" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H200" s="5" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="G201" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H201" s="5" t="inlineStr">
@@ -10303,7 +10303,7 @@
       </c>
       <c r="G202" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H202" s="5" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="G203" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H203" s="5" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="G204" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H204" s="5" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="G205" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H205" s="5" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="G207" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H207" s="5" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="G208" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H208" s="5" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="G209" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H209" s="5" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="G210" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H210" s="5" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="G221" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H221" s="5" t="inlineStr">
@@ -11227,7 +11227,7 @@
       </c>
       <c r="G222" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H222" s="5" t="inlineStr">
@@ -11317,7 +11317,7 @@
       </c>
       <c r="G224" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H224" s="5" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="G225" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H225" s="5" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="G226" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H226" s="5" t="inlineStr">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="G227" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H227" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11595,7 +11595,7 @@
       </c>
       <c r="G230" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H230" s="5" t="inlineStr">
@@ -11642,7 +11642,7 @@
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H231" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -11736,7 +11736,7 @@
       </c>
       <c r="G233" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H233" s="5" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 160715@med.asu.edu.eg</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="G236" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H236" s="5" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H237" s="5" t="inlineStr">
@@ -11971,7 +11971,7 @@
       </c>
       <c r="G238" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H238" s="5" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="G241" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H241" s="5" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="G242" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H242" s="5" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="G243" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H243" s="5" t="inlineStr">
@@ -12245,7 +12245,7 @@
       </c>
       <c r="G244" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H244" s="5" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H245" s="5" t="inlineStr">
@@ -12339,7 +12339,7 @@
       </c>
       <c r="G246" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H246" s="5" t="inlineStr">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="G247" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H247" s="5" t="inlineStr">
@@ -12433,7 +12433,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H249" s="5" t="inlineStr">
@@ -12527,7 +12527,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H251" s="5" t="inlineStr">
@@ -12664,7 +12664,7 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
@@ -12711,7 +12711,7 @@
       </c>
       <c r="G254" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H254" s="5" t="inlineStr">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr">
@@ -12805,7 +12805,7 @@
       </c>
       <c r="G256" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H256" s="5" t="inlineStr">
@@ -12852,7 +12852,7 @@
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H257" s="5" t="inlineStr">
@@ -12985,7 +12985,7 @@
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H260" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H262" s="5" t="inlineStr">
@@ -13126,7 +13126,7 @@
       </c>
       <c r="G263" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H263" s="5" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="G264" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H264" s="5" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="G265" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H265" s="5" t="inlineStr">
@@ -13310,7 +13310,7 @@
       </c>
       <c r="G267" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H267" s="5" t="inlineStr">
@@ -13357,7 +13357,7 @@
       </c>
       <c r="G268" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H268" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2027/2028</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2027/2028, 2026/2027</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -13588,7 +13588,7 @@
       </c>
       <c r="G273" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Alyaa Sheir</t>
         </is>
       </c>
       <c r="H273" s="5" t="inlineStr">
@@ -13635,7 +13635,7 @@
       </c>
       <c r="G274" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H274" s="5" t="inlineStr">
@@ -13682,7 +13682,7 @@
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H275" s="5" t="inlineStr">
@@ -13729,7 +13729,7 @@
       </c>
       <c r="G276" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H276" s="5" t="inlineStr">
@@ -13776,7 +13776,7 @@
       </c>
       <c r="G277" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H277" s="5" t="inlineStr">
@@ -14038,7 +14038,7 @@
       </c>
       <c r="G283" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H283" s="5" t="inlineStr">
@@ -14085,7 +14085,7 @@
       </c>
       <c r="G284" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H284" s="5" t="inlineStr">
@@ -14132,7 +14132,7 @@
       </c>
       <c r="G285" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H285" s="5" t="inlineStr">
@@ -14179,7 +14179,7 @@
       </c>
       <c r="G286" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H286" s="5" t="inlineStr">
@@ -14226,7 +14226,7 @@
       </c>
       <c r="G287" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H287" s="5" t="inlineStr">
@@ -14273,7 +14273,7 @@
       </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H288" s="5" t="inlineStr">
@@ -14320,7 +14320,7 @@
       </c>
       <c r="G289" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H289" s="5" t="inlineStr">
@@ -14367,7 +14367,7 @@
       </c>
       <c r="G290" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H290" s="5" t="inlineStr">
@@ -14414,7 +14414,7 @@
       </c>
       <c r="G291" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H291" s="5" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
@@ -14551,7 +14551,7 @@
       </c>
       <c r="G294" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H294" s="5" t="inlineStr">
@@ -14598,7 +14598,7 @@
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H295" s="5" t="inlineStr">
@@ -14645,7 +14645,7 @@
       </c>
       <c r="G296" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H296" s="5" t="inlineStr">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H297" s="5" t="inlineStr">
@@ -14739,7 +14739,7 @@
       </c>
       <c r="G298" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H298" s="5" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="G300" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H300" s="5" t="inlineStr">
@@ -14876,7 +14876,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
@@ -14970,7 +14970,7 @@
       </c>
       <c r="G303" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H303" s="5" t="inlineStr">
@@ -15017,7 +15017,7 @@
       </c>
       <c r="G304" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H304" s="5" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="G305" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H305" s="5" t="inlineStr">
@@ -15111,7 +15111,7 @@
       </c>
       <c r="G306" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H306" s="5" t="inlineStr">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="G307" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H307" s="5" t="inlineStr">
@@ -15205,7 +15205,7 @@
       </c>
       <c r="G308" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H308" s="5" t="inlineStr">
@@ -15252,7 +15252,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2027/2028</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15346,7 +15346,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2027/2028, 2026/2027</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">
@@ -15436,7 +15436,7 @@
       </c>
       <c r="G313" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Alyaa Sheir</t>
         </is>
       </c>
       <c r="H313" s="5" t="inlineStr">
@@ -15483,7 +15483,7 @@
       </c>
       <c r="G314" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H314" s="5" t="inlineStr">
@@ -15530,7 +15530,7 @@
       </c>
       <c r="G315" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H315" s="5" t="inlineStr">
@@ -15577,7 +15577,7 @@
       </c>
       <c r="G316" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H316" s="5" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="G317" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H317" s="5" t="inlineStr">
@@ -15671,7 +15671,7 @@
       </c>
       <c r="G318" s="5" t="inlineStr">
         <is>
-          <t>2027/2028</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H318" s="5" t="inlineStr">
@@ -15804,7 +15804,7 @@
       </c>
       <c r="G321" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H321" s="5" t="inlineStr">
@@ -15851,7 +15851,7 @@
       </c>
       <c r="G322" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H322" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -725,7 +725,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H76" s="5" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H78" s="5" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H82" s="5" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H84" s="5" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H86" s="5" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H90" s="5" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H91" s="5" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H92" s="5" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Developer, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H96" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H104" s="5" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H106" s="5" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H108" s="5" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H112" s="5" t="inlineStr">
@@ -6172,7 +6172,7 @@
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H113" s="5" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H114" s="5" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H116" s="5" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H120" s="5" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H122" s="5" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H126" s="5" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H132" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Developer, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H144" s="5" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dou7a</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H146" s="5" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="G148" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H148" s="5" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="G152" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H152" s="5" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H154" s="5" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="G156" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H156" s="5" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H158" s="5" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="G160" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H160" s="5" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="G164" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H164" s="5" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H167" s="5" t="inlineStr">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="G168" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H168" s="5" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H169" s="5" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H170" s="5" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H175" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H181" s="5" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="G182" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H182" s="5" t="inlineStr">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="G183" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H183" s="5" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H185" s="5" t="inlineStr">
@@ -9555,7 +9555,7 @@
       </c>
       <c r="G186" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H186" s="5" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="G187" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H187" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="G190" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H190" s="5" t="inlineStr">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="G191" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H191" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="G193" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H193" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>160715@med.asu.edu.eg, 2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
@@ -10021,7 +10021,7 @@
       </c>
       <c r="G196" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H196" s="5" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="G197" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H197" s="5" t="inlineStr">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="G198" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H198" s="5" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="G200" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H200" s="5" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="G201" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H201" s="5" t="inlineStr">
@@ -10303,7 +10303,7 @@
       </c>
       <c r="G202" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H202" s="5" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="G203" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H203" s="5" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="G204" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H204" s="5" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="G205" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H205" s="5" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="G207" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H207" s="5" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="G208" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H208" s="5" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="G209" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H209" s="5" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="G210" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H210" s="5" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="G221" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H221" s="5" t="inlineStr">
@@ -11227,7 +11227,7 @@
       </c>
       <c r="G222" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H222" s="5" t="inlineStr">
@@ -11317,7 +11317,7 @@
       </c>
       <c r="G224" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H224" s="5" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="G225" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H225" s="5" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="G226" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H226" s="5" t="inlineStr">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="G227" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H227" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11595,7 +11595,7 @@
       </c>
       <c r="G230" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H230" s="5" t="inlineStr">
@@ -11642,7 +11642,7 @@
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H231" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -11736,7 +11736,7 @@
       </c>
       <c r="G233" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H233" s="5" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>160715@med.asu.edu.eg, 2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="G236" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H236" s="5" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H237" s="5" t="inlineStr">
@@ -11971,7 +11971,7 @@
       </c>
       <c r="G238" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H238" s="5" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="G241" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H241" s="5" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="G242" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H242" s="5" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="G243" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H243" s="5" t="inlineStr">
@@ -12245,7 +12245,7 @@
       </c>
       <c r="G244" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H244" s="5" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H245" s="5" t="inlineStr">
@@ -12339,7 +12339,7 @@
       </c>
       <c r="G246" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H246" s="5" t="inlineStr">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="G247" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H247" s="5" t="inlineStr">
@@ -12433,7 +12433,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H249" s="5" t="inlineStr">
@@ -12527,7 +12527,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H251" s="5" t="inlineStr">
@@ -12664,7 +12664,7 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
@@ -12711,7 +12711,7 @@
       </c>
       <c r="G254" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H254" s="5" t="inlineStr">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr">
@@ -12805,7 +12805,7 @@
       </c>
       <c r="G256" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H256" s="5" t="inlineStr">
@@ -12852,7 +12852,7 @@
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H257" s="5" t="inlineStr">
@@ -12985,7 +12985,7 @@
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H260" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H262" s="5" t="inlineStr">
@@ -13126,7 +13126,7 @@
       </c>
       <c r="G263" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H263" s="5" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="G264" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H264" s="5" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="G265" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H265" s="5" t="inlineStr">
@@ -13310,7 +13310,7 @@
       </c>
       <c r="G267" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H267" s="5" t="inlineStr">
@@ -13357,7 +13357,7 @@
       </c>
       <c r="G268" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H268" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2025/2026</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2026/2027, 2025/2026</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -13588,7 +13588,7 @@
       </c>
       <c r="G273" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Alyaa Sheir</t>
         </is>
       </c>
       <c r="H273" s="5" t="inlineStr">
@@ -13635,7 +13635,7 @@
       </c>
       <c r="G274" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H274" s="5" t="inlineStr">
@@ -13682,7 +13682,7 @@
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H275" s="5" t="inlineStr">
@@ -13729,7 +13729,7 @@
       </c>
       <c r="G276" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H276" s="5" t="inlineStr">
@@ -13776,7 +13776,7 @@
       </c>
       <c r="G277" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H277" s="5" t="inlineStr">
@@ -14038,7 +14038,7 @@
       </c>
       <c r="G283" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H283" s="5" t="inlineStr">
@@ -14085,7 +14085,7 @@
       </c>
       <c r="G284" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H284" s="5" t="inlineStr">
@@ -14132,7 +14132,7 @@
       </c>
       <c r="G285" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H285" s="5" t="inlineStr">
@@ -14179,7 +14179,7 @@
       </c>
       <c r="G286" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H286" s="5" t="inlineStr">
@@ -14226,7 +14226,7 @@
       </c>
       <c r="G287" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H287" s="5" t="inlineStr">
@@ -14273,7 +14273,7 @@
       </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H288" s="5" t="inlineStr">
@@ -14320,7 +14320,7 @@
       </c>
       <c r="G289" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H289" s="5" t="inlineStr">
@@ -14367,7 +14367,7 @@
       </c>
       <c r="G290" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H290" s="5" t="inlineStr">
@@ -14414,7 +14414,7 @@
       </c>
       <c r="G291" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H291" s="5" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
@@ -14551,7 +14551,7 @@
       </c>
       <c r="G294" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H294" s="5" t="inlineStr">
@@ -14598,7 +14598,7 @@
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H295" s="5" t="inlineStr">
@@ -14645,7 +14645,7 @@
       </c>
       <c r="G296" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H296" s="5" t="inlineStr">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H297" s="5" t="inlineStr">
@@ -14739,7 +14739,7 @@
       </c>
       <c r="G298" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H298" s="5" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="G300" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H300" s="5" t="inlineStr">
@@ -14876,7 +14876,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
@@ -14970,7 +14970,7 @@
       </c>
       <c r="G303" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H303" s="5" t="inlineStr">
@@ -15017,7 +15017,7 @@
       </c>
       <c r="G304" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H304" s="5" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="G305" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H305" s="5" t="inlineStr">
@@ -15111,7 +15111,7 @@
       </c>
       <c r="G306" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H306" s="5" t="inlineStr">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="G307" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H307" s="5" t="inlineStr">
@@ -15205,7 +15205,7 @@
       </c>
       <c r="G308" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H308" s="5" t="inlineStr">
@@ -15252,7 +15252,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2025/2026</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15346,7 +15346,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>2027/2028, 2026/2027, 2025/2026</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">
@@ -15436,7 +15436,7 @@
       </c>
       <c r="G313" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Alyaa Sheir</t>
         </is>
       </c>
       <c r="H313" s="5" t="inlineStr">
@@ -15483,7 +15483,7 @@
       </c>
       <c r="G314" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H314" s="5" t="inlineStr">
@@ -15530,7 +15530,7 @@
       </c>
       <c r="G315" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H315" s="5" t="inlineStr">
@@ -15577,7 +15577,7 @@
       </c>
       <c r="G316" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H316" s="5" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="G317" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H317" s="5" t="inlineStr">
@@ -15671,7 +15671,7 @@
       </c>
       <c r="G318" s="5" t="inlineStr">
         <is>
-          <t>2027/2028</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H318" s="5" t="inlineStr">
@@ -15804,7 +15804,7 @@
       </c>
       <c r="G321" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H321" s="5" t="inlineStr">
@@ -15851,7 +15851,7 @@
       </c>
       <c r="G322" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H322" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -15252,7 +15252,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15346,7 +15346,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -14876,7 +14876,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15346,7 +15346,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Developer</t>
+          <t>Developer, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Developer</t>
+          <t>Developer, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -14876,7 +14876,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Developer</t>
+          <t>Developer, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Developer</t>
+          <t>Developer, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -15252,7 +15252,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15346,7 +15346,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -14876,7 +14876,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -14876,7 +14876,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="7">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">
@@ -961,7 +961,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>82.2%</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>77.7%</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>75.8%</t>
         </is>
       </c>
     </row>
@@ -1803,22 +1803,22 @@
         <v>40</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>78.9%</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="H202" s="5" t="inlineStr">
         <is>
-          <t>27/37</t>
+          <t>32/37</t>
         </is>
       </c>
       <c r="I202" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -13963,45 +13963,49 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B282" s="2" t="inlineStr">
+      <c r="A282" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B282" s="5" t="inlineStr">
         <is>
           <t>A2D1</t>
         </is>
       </c>
-      <c r="C282" s="2" t="inlineStr">
+      <c r="C282" s="5" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D282" s="2" t="inlineStr">
+      <c r="D282" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E282" s="2" t="inlineStr">
+      <c r="E282" s="5" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F282" s="2" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G282" s="2" t="inlineStr"/>
-      <c r="H282" s="2" t="inlineStr">
-        <is>
-          <t>0/34</t>
-        </is>
-      </c>
-      <c r="I282" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F282" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G282" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Tasneem El-Sayed</t>
+        </is>
+      </c>
+      <c r="H282" s="5" t="inlineStr">
+        <is>
+          <t>29/34</t>
+        </is>
+      </c>
+      <c r="I282" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -15252,7 +15256,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15299,7 +15303,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15346,7 +15350,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Developer</t>
+          <t>Developer, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Developer</t>
+          <t>Developer, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Developer</t>
+          <t>Developer, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Developer</t>
+          <t>Developer, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Developer</t>
+          <t>Developer, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Developer</t>
+          <t>Developer, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Developer</t>
+          <t>Developer, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Developer</t>
+          <t>Developer, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Developer</t>
+          <t>Developer, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Developer</t>
+          <t>Developer, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Developer</t>
+          <t>Developer, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Developer</t>
+          <t>Developer, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Developer</t>
+          <t>Developer, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Developer</t>
+          <t>Developer, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Developer</t>
+          <t>Developer, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Developer</t>
+          <t>Developer, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Developer</t>
+          <t>Developer, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Developer</t>
+          <t>Developer, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Developer</t>
+          <t>Developer, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Developer</t>
+          <t>Developer, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Developer</t>
+          <t>Developer, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Developer, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Developer</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_A2_session_analysis.xlsx
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Developer, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Developer</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">
